--- a/plantillas/plantilla.xlsx
+++ b/plantillas/plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00.- JEJ\01.- WORKS 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{B13872B7-BAF0-488B-AE47-9646A72CA8B3}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{A52C23F2-CD2F-4607-AFA9-048949D5917D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="171" uniqueCount="154">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="170" uniqueCount="153">
   <si>
     <t>Longitudes</t>
   </si>
@@ -160,9 +160,6 @@
   </si>
   <si>
     <t xml:space="preserve">Calles Zanja </t>
-  </si>
-  <si>
-    <t>obs:No se logra instalar VoD en tiro 5 Parada 9 , ya que se encontraba cargado al momento de llegada de personal JEJ.</t>
   </si>
   <si>
     <t>Arañas Inferiores</t>
@@ -3382,9 +3379,7 @@
       </c>
       <c r="N7" s="226"/>
       <c r="O7" s="228"/>
-      <c r="P7" s="236" t="s">
-        <v>27</v>
-      </c>
+      <c r="P7" s="236"/>
       <c r="Q7" s="237"/>
       <c r="R7" s="237"/>
       <c r="S7" s="237"/>
@@ -3395,7 +3390,7 @@
       <c r="X7" s="238"/>
       <c r="Y7" s="101"/>
       <c r="AA7" s="94" t="s">
-        <v>28</v>
+        <v>27</v>
       </c>
       <c r="AB7" s="96" t="str">
         <f>IF(COUNTIF(I16:I82,"Roto")=0,"",COUNTIF(AC17:AC83,"ok")/COUNTIF(I17:I83,"Roto"))</f>
@@ -3404,21 +3399,24 @@
     </row>
     <row r="8" spans="2:51" ht="45" customHeight="1">
       <c r="B8" s="150" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
       <c r="C8" s="151"/>
       <c r="D8" s="151"/>
       <c r="E8" s="152"/>
       <c r="F8" s="173" t="s">
-        <v>30</v>
+        <v>29</v>
       </c>
       <c r="G8" s="174"/>
       <c r="H8" s="134"/>
       <c r="I8" s="177" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
       <c r="J8" s="178"/>
-      <c r="K8" s="179"/>
+      <c r="K8" s="179">
+        <f>IF(AO34=0,"",AO34)</f>
+        <v>124</v>
+      </c>
       <c r="L8" s="180"/>
       <c r="M8" s="172"/>
       <c r="N8" s="227"/>
@@ -3434,7 +3432,7 @@
       <c r="X8" s="235"/>
       <c r="Y8" s="101"/>
       <c r="AA8" s="94" t="s">
-        <v>32</v>
+        <v>31</v>
       </c>
       <c r="AB8" s="96" t="str">
         <f>IF(COUNTIF(I16:I82,"Roto")=0,"",COUNTIF(AE17:AE83,"ok")/COUNTIF(I17:I83,"Roto"))</f>
@@ -3443,24 +3441,27 @@
     </row>
     <row r="9" spans="2:51" ht="45" customHeight="1" thickBot="1">
       <c r="B9" s="150" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
       <c r="C9" s="151"/>
       <c r="D9" s="151"/>
       <c r="E9" s="258"/>
       <c r="F9" s="153" t="s">
-        <v>34</v>
+        <v>33</v>
       </c>
       <c r="G9" s="154"/>
       <c r="H9" s="135"/>
       <c r="I9" s="251" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
       <c r="J9" s="252"/>
-      <c r="K9" s="277"/>
+      <c r="K9" s="277">
+        <f>IF(AP34=0,"",AP34)</f>
+        <v>2397.2800000000002</v>
+      </c>
       <c r="L9" s="278"/>
       <c r="M9" s="104" t="s">
-        <v>36</v>
+        <v>35</v>
       </c>
       <c r="N9" s="256"/>
       <c r="O9" s="257"/>
@@ -3475,7 +3476,7 @@
       <c r="X9" s="235"/>
       <c r="Y9" s="101"/>
       <c r="AA9" s="94" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="AB9" s="96" t="str">
         <f>IF(COUNTIF(I16:I82,"Roto")=0,"",COUNTIF(AG17:AG83,"ok")/COUNTIF(I17:I83,"Roto"))</f>
@@ -3484,24 +3485,30 @@
     </row>
     <row r="10" spans="2:51" ht="45" customHeight="1">
       <c r="B10" s="150" t="s">
-        <v>38</v>
+        <v>37</v>
       </c>
       <c r="C10" s="151"/>
       <c r="D10" s="151"/>
       <c r="E10" s="258"/>
       <c r="F10" s="153" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
       <c r="G10" s="154"/>
       <c r="H10" s="135"/>
       <c r="I10" s="251" t="s">
+        <v>39</v>
+      </c>
+      <c r="J10" s="252"/>
+      <c r="K10" s="105" t="str">
+        <f>IF($AW$34=0,"",9/$AW$34)</f>
+        <v/>
+      </c>
+      <c r="L10" s="106" t="str">
+        <f>IF(K10="","",IF(K10&gt;=K11,IF(K10&lt;=L11,"Ok","Fuera de Rango Alto"),"Fuera de Rango Bajo"))</f>
+        <v/>
+      </c>
+      <c r="M10" s="267" t="s">
         <v>40</v>
-      </c>
-      <c r="J10" s="252"/>
-      <c r="K10" s="105"/>
-      <c r="L10" s="106"/>
-      <c r="M10" s="267" t="s">
-        <v>41</v>
       </c>
       <c r="N10" s="202"/>
       <c r="O10" s="127"/>
@@ -3516,57 +3523,63 @@
       <c r="X10" s="232"/>
       <c r="Y10" s="102"/>
       <c r="AA10" s="94" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="AB10" s="96" t="str">
         <f>IF(COUNTIF(I16:I82,"Roto")=0,"",COUNTIF(AI17:AI83,"ok")/COUNTIF(I17:I83,"Roto"))</f>
         <v/>
       </c>
       <c r="AL10" s="15" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="AM10" s="97">
         <v>21.16</v>
       </c>
       <c r="AN10" s="16" t="s">
+        <v>43</v>
+      </c>
+      <c r="AR10" s="37" t="s">
         <v>44</v>
-      </c>
-      <c r="AR10" s="37" t="s">
-        <v>45</v>
       </c>
       <c r="AS10" s="24">
         <f>AN5</f>
         <v>0</v>
       </c>
       <c r="AT10" s="25" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="11" spans="2:51" ht="45" customHeight="1" thickBot="1">
       <c r="B11" s="255" t="s">
-        <v>47</v>
+        <v>46</v>
       </c>
       <c r="C11" s="216"/>
       <c r="D11" s="216"/>
       <c r="E11" s="259"/>
       <c r="F11" s="275" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
       <c r="G11" s="276"/>
       <c r="H11" s="136"/>
       <c r="I11" s="211" t="s">
+        <v>48</v>
+      </c>
+      <c r="J11" s="212"/>
+      <c r="K11" s="108" t="str">
+        <f>IF(H14="","",AQ4*PI()*(H14*25.4/2000)^2)</f>
+        <v/>
+      </c>
+      <c r="L11" s="109" t="str">
+        <f>IF(H14="","",AQ5*PI()*(H14*25.4/2000)^2)</f>
+        <v/>
+      </c>
+      <c r="M11" s="172" t="s">
         <v>49</v>
-      </c>
-      <c r="J11" s="212"/>
-      <c r="K11" s="108"/>
-      <c r="L11" s="109"/>
-      <c r="M11" s="172" t="s">
-        <v>50</v>
       </c>
       <c r="N11" s="204"/>
       <c r="O11" s="128"/>
       <c r="P11" s="239" t="s">
-        <v>51</v>
+        <v>50</v>
       </c>
       <c r="Q11" s="240"/>
       <c r="R11" s="240"/>
@@ -3580,53 +3593,62 @@
         <v>21</v>
       </c>
       <c r="AA11" s="94" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
       <c r="AB11" s="96" t="str">
         <f>IF(COUNTIF(I16:I82,"Roto")=0,"",COUNTIF(AK17:AK83,"ok")/COUNTIF(I17:I83,"Roto"))</f>
         <v/>
       </c>
       <c r="AL11" s="17" t="s">
-        <v>53</v>
+        <v>52</v>
       </c>
       <c r="AM11" s="80">
         <f>H14</f>
         <v>0</v>
       </c>
       <c r="AN11" s="18" t="s">
+        <v>53</v>
+      </c>
+      <c r="AR11" s="183" t="s">
         <v>54</v>
-      </c>
-      <c r="AR11" s="183" t="s">
-        <v>55</v>
       </c>
       <c r="AS11" s="184"/>
       <c r="AT11" s="185"/>
       <c r="AU11" s="183" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
       <c r="AV11" s="184"/>
       <c r="AW11" s="185"/>
     </row>
     <row r="12" spans="2:51" ht="45" customHeight="1">
       <c r="B12" s="253" t="s">
-        <v>57</v>
+        <v>56</v>
       </c>
       <c r="C12" s="254"/>
       <c r="D12" s="260"/>
       <c r="E12" s="261"/>
       <c r="F12" s="273" t="s">
+        <v>57</v>
+      </c>
+      <c r="G12" s="274"/>
+      <c r="H12" s="86" t="str">
+        <f>IF(H11="","",IF(H8="","",H11-H8))</f>
+        <v/>
+      </c>
+      <c r="I12" s="213" t="s">
         <v>58</v>
       </c>
-      <c r="G12" s="274"/>
-      <c r="H12" s="86"/>
-      <c r="I12" s="213" t="s">
+      <c r="J12" s="214"/>
+      <c r="K12" s="107" t="str">
+        <f>IF(SUM(F17:F83)=0,"",(SUM(F17:F83)-SUM(G17:G83))*K11)</f>
+        <v/>
+      </c>
+      <c r="L12" s="107" t="str">
+        <f>IF(SUM(G17:G83)=0,"",(SUM(G17:G83)-SUM(H17:H83))*L11)</f>
+        <v/>
+      </c>
+      <c r="M12" s="268" t="s">
         <v>59</v>
-      </c>
-      <c r="J12" s="214"/>
-      <c r="K12" s="107"/>
-      <c r="L12" s="107"/>
-      <c r="M12" s="268" t="s">
-        <v>60</v>
       </c>
       <c r="N12" s="269"/>
       <c r="O12" s="129"/>
@@ -3641,55 +3663,58 @@
       <c r="X12" s="238"/>
       <c r="Y12" s="101"/>
       <c r="AL12" s="17" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="AM12" s="5">
         <v>825</v>
       </c>
       <c r="AN12" s="18" t="s">
+        <v>61</v>
+      </c>
+      <c r="AR12" s="28" t="s">
         <v>62</v>
-      </c>
-      <c r="AR12" s="28" t="s">
-        <v>63</v>
       </c>
       <c r="AS12" s="23">
         <f>AS10*AM14</f>
         <v>0</v>
       </c>
       <c r="AT12" s="27" t="s">
+        <v>63</v>
+      </c>
+      <c r="AU12" s="28" t="s">
         <v>64</v>
-      </c>
-      <c r="AU12" s="28" t="s">
-        <v>65</v>
       </c>
       <c r="AV12" s="23">
         <f>AO34*AM10</f>
         <v>2623.84</v>
       </c>
       <c r="AW12" s="27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="13" spans="2:51" ht="45" customHeight="1">
       <c r="B13" s="264" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="C13" s="265"/>
       <c r="D13" s="262"/>
       <c r="E13" s="263"/>
       <c r="F13" s="272" t="s">
+        <v>66</v>
+      </c>
+      <c r="G13" s="215"/>
+      <c r="H13" s="87" t="str">
+        <f>IF(H10="","",IF(H9="","",H10-H9))</f>
+        <v/>
+      </c>
+      <c r="I13" s="209" t="s">
         <v>67</v>
-      </c>
-      <c r="G13" s="215"/>
-      <c r="H13" s="87"/>
-      <c r="I13" s="209" t="s">
-        <v>68</v>
       </c>
       <c r="J13" s="210"/>
       <c r="K13" s="270"/>
       <c r="L13" s="271"/>
       <c r="M13" s="202" t="s">
-        <v>69</v>
+        <v>68</v>
       </c>
       <c r="N13" s="203"/>
       <c r="O13" s="130"/>
@@ -3704,36 +3729,36 @@
       <c r="X13" s="235"/>
       <c r="Y13" s="115"/>
       <c r="AL13" s="17" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="AM13" s="88">
         <v>0.02</v>
       </c>
       <c r="AN13" s="18" t="s">
+        <v>70</v>
+      </c>
+      <c r="AR13" s="28" t="s">
         <v>71</v>
-      </c>
-      <c r="AR13" s="28" t="s">
-        <v>72</v>
       </c>
       <c r="AS13" s="23">
         <f>AS12*(1+$AM$13)</f>
         <v>0</v>
       </c>
       <c r="AT13" s="27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AU13" s="28" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
       <c r="AV13" s="23">
         <f>AV12*(1-$AM$13)</f>
         <v>2571.3632000000002</v>
       </c>
       <c r="AW13" s="27" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="AX13" s="28" t="s">
-        <v>74</v>
+        <v>73</v>
       </c>
       <c r="AY13" s="23">
         <f>AS12-AV13</f>
@@ -3742,24 +3767,24 @@
     </row>
     <row r="14" spans="2:51" ht="45" customHeight="1" thickBot="1">
       <c r="B14" s="157" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
       <c r="C14" s="158"/>
       <c r="D14" s="270"/>
       <c r="E14" s="271"/>
       <c r="F14" s="195" t="s">
-        <v>76</v>
+        <v>75</v>
       </c>
       <c r="G14" s="196"/>
       <c r="H14" s="85"/>
       <c r="I14" s="199" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="J14" s="200"/>
       <c r="K14" s="220"/>
       <c r="L14" s="221"/>
       <c r="M14" s="154" t="s">
-        <v>78</v>
+        <v>77</v>
       </c>
       <c r="N14" s="201"/>
       <c r="O14" s="131"/>
@@ -3774,7 +3799,7 @@
       <c r="X14" s="235"/>
       <c r="Y14" s="101"/>
       <c r="Z14" s="217" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
       <c r="AA14" s="218"/>
       <c r="AB14" s="218"/>
@@ -3787,17 +3812,17 @@
       <c r="AI14" s="218"/>
       <c r="AJ14" s="219"/>
       <c r="AL14" s="17" t="s">
-        <v>80</v>
+        <v>79</v>
       </c>
       <c r="AM14" s="6">
         <f>AM12*PI()*(AM11*25.4/2000)^2</f>
         <v>0</v>
       </c>
       <c r="AN14" s="18" t="s">
+        <v>80</v>
+      </c>
+      <c r="AR14" s="28" t="s">
         <v>81</v>
-      </c>
-      <c r="AR14" s="28" t="s">
-        <v>82</v>
       </c>
       <c r="AS14" s="89">
         <f>AS12/$AM$10</f>
@@ -3805,7 +3830,7 @@
       </c>
       <c r="AT14" s="27"/>
       <c r="AU14" s="28" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
       <c r="AV14" s="89">
         <f>AV13/$AM$10</f>
@@ -3813,7 +3838,7 @@
       </c>
       <c r="AW14" s="27"/>
       <c r="AX14" s="28" t="s">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="AY14" s="23">
         <f>AS14-AV14</f>
@@ -3822,24 +3847,24 @@
     </row>
     <row r="15" spans="2:51" ht="54">
       <c r="B15" s="164" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
       <c r="C15" s="165"/>
       <c r="D15" s="193"/>
       <c r="E15" s="194"/>
       <c r="F15" s="207" t="s">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="G15" s="208"/>
       <c r="H15" s="125"/>
       <c r="I15" s="197" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
       <c r="J15" s="198"/>
       <c r="K15" s="193"/>
       <c r="L15" s="194"/>
       <c r="M15" s="215" t="s">
-        <v>88</v>
+        <v>87</v>
       </c>
       <c r="N15" s="216"/>
       <c r="O15" s="87" t="str">
@@ -3857,40 +3882,40 @@
       <c r="X15" s="232"/>
       <c r="Y15" s="103"/>
       <c r="Z15" s="140" t="s">
+        <v>88</v>
+      </c>
+      <c r="AA15" s="206" t="s">
         <v>89</v>
-      </c>
-      <c r="AA15" s="206" t="s">
-        <v>90</v>
       </c>
       <c r="AB15" s="206"/>
       <c r="AC15" s="205" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
       <c r="AD15" s="205"/>
       <c r="AE15" s="206" t="s">
-        <v>92</v>
+        <v>91</v>
       </c>
       <c r="AF15" s="206"/>
       <c r="AG15" s="205" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
       <c r="AH15" s="205"/>
       <c r="AI15" s="206" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
       <c r="AJ15" s="225"/>
       <c r="AL15" s="19" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
       <c r="AM15" s="33" t="e">
         <f>(16*$AM$10)/$AM$14</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AN15" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AR15" s="28" t="s">
-        <v>96</v>
+        <v>95</v>
       </c>
       <c r="AS15" s="89">
         <f>(AS12*$AM$13)/$AM$10</f>
@@ -3898,7 +3923,7 @@
       </c>
       <c r="AT15" s="27"/>
       <c r="AU15" s="28" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="AV15" s="89">
         <f>(AV12*$AM$13)/$AM$10</f>
@@ -3908,126 +3933,126 @@
     </row>
     <row r="16" spans="2:51" ht="75" customHeight="1" thickBot="1">
       <c r="B16" s="124" t="s">
+        <v>97</v>
+      </c>
+      <c r="C16" s="123" t="s">
         <v>98</v>
       </c>
-      <c r="C16" s="123" t="s">
+      <c r="D16" s="123" t="s">
         <v>99</v>
       </c>
-      <c r="D16" s="123" t="s">
+      <c r="E16" s="116" t="s">
         <v>100</v>
       </c>
-      <c r="E16" s="116" t="s">
+      <c r="F16" s="123" t="s">
         <v>101</v>
       </c>
-      <c r="F16" s="123" t="s">
+      <c r="G16" s="116" t="s">
         <v>102</v>
       </c>
-      <c r="G16" s="116" t="s">
+      <c r="H16" s="117" t="s">
         <v>103</v>
       </c>
-      <c r="H16" s="117" t="s">
+      <c r="I16" s="116" t="s">
         <v>104</v>
       </c>
-      <c r="I16" s="116" t="s">
+      <c r="J16" s="116" t="s">
         <v>105</v>
       </c>
-      <c r="J16" s="116" t="s">
+      <c r="K16" s="116" t="s">
         <v>106</v>
       </c>
-      <c r="K16" s="116" t="s">
+      <c r="L16" s="116" t="s">
         <v>107</v>
       </c>
-      <c r="L16" s="116" t="s">
+      <c r="M16" s="137" t="s">
         <v>108</v>
       </c>
-      <c r="M16" s="137" t="s">
+      <c r="N16" s="138" t="s">
         <v>109</v>
       </c>
-      <c r="N16" s="138" t="s">
+      <c r="O16" s="118" t="s">
         <v>110</v>
       </c>
-      <c r="O16" s="118" t="s">
+      <c r="P16" s="118" t="s">
         <v>111</v>
       </c>
-      <c r="P16" s="118" t="s">
+      <c r="Q16" s="118" t="s">
         <v>112</v>
       </c>
-      <c r="Q16" s="118" t="s">
+      <c r="R16" s="116" t="s">
         <v>113</v>
       </c>
-      <c r="R16" s="116" t="s">
+      <c r="S16" s="116" t="s">
         <v>114</v>
       </c>
-      <c r="S16" s="116" t="s">
+      <c r="T16" s="116" t="s">
+        <v>112</v>
+      </c>
+      <c r="U16" s="138" t="s">
         <v>115</v>
       </c>
-      <c r="T16" s="116" t="s">
-        <v>113</v>
-      </c>
-      <c r="U16" s="138" t="s">
+      <c r="V16" s="139" t="s">
         <v>116</v>
       </c>
-      <c r="V16" s="139" t="s">
+      <c r="W16" s="121" t="s">
         <v>117</v>
       </c>
-      <c r="W16" s="121" t="s">
+      <c r="X16" s="121" t="s">
         <v>118</v>
       </c>
-      <c r="X16" s="121" t="s">
+      <c r="Y16" s="121" t="s">
         <v>119</v>
       </c>
-      <c r="Y16" s="121" t="s">
+      <c r="Z16" s="122" t="s">
         <v>120</v>
       </c>
-      <c r="Z16" s="122" t="s">
+      <c r="AA16" s="145" t="s">
         <v>121</v>
       </c>
-      <c r="AA16" s="145" t="s">
+      <c r="AB16" s="145" t="s">
         <v>122</v>
       </c>
-      <c r="AB16" s="145" t="s">
+      <c r="AC16" s="142" t="s">
+        <v>121</v>
+      </c>
+      <c r="AD16" s="145" t="s">
+        <v>122</v>
+      </c>
+      <c r="AE16" s="141" t="s">
+        <v>121</v>
+      </c>
+      <c r="AF16" s="145" t="s">
+        <v>122</v>
+      </c>
+      <c r="AG16" s="142" t="s">
+        <v>121</v>
+      </c>
+      <c r="AH16" s="145" t="s">
+        <v>122</v>
+      </c>
+      <c r="AI16" s="141" t="s">
+        <v>121</v>
+      </c>
+      <c r="AJ16" s="145" t="s">
         <v>123</v>
       </c>
-      <c r="AC16" s="142" t="s">
-        <v>122</v>
-      </c>
-      <c r="AD16" s="145" t="s">
-        <v>123</v>
-      </c>
-      <c r="AE16" s="141" t="s">
-        <v>122</v>
-      </c>
-      <c r="AF16" s="145" t="s">
-        <v>123</v>
-      </c>
-      <c r="AG16" s="142" t="s">
-        <v>122</v>
-      </c>
-      <c r="AH16" s="145" t="s">
-        <v>123</v>
-      </c>
-      <c r="AI16" s="141" t="s">
-        <v>122</v>
-      </c>
-      <c r="AJ16" s="145" t="s">
+      <c r="AK16" s="143" t="s">
+        <v>121</v>
+      </c>
+      <c r="AM16" s="19" t="s">
         <v>124</v>
-      </c>
-      <c r="AK16" s="143" t="s">
-        <v>122</v>
-      </c>
-      <c r="AM16" s="19" t="s">
-        <v>125</v>
       </c>
       <c r="AN16" s="33" t="e">
         <f>(17*$AM$10)/AM14</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AO16" s="20" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
       <c r="AQ16" s="69"/>
       <c r="AS16" s="49" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
       <c r="AT16" s="31">
         <f>SUM(AS14:AS15)</f>
@@ -4035,7 +4060,7 @@
       </c>
       <c r="AU16" s="30"/>
       <c r="AV16" s="49" t="s">
-        <v>127</v>
+        <v>126</v>
       </c>
       <c r="AW16" s="31">
         <f>SUM(AV14:AV15)</f>
@@ -4053,7 +4078,10 @@
       <c r="E17" s="112"/>
       <c r="F17" s="112"/>
       <c r="G17" s="112"/>
-      <c r="H17" s="113"/>
+      <c r="H17" s="113">
+        <f>F17-G17</f>
+        <v>0</v>
+      </c>
       <c r="I17" s="99"/>
       <c r="J17" s="99"/>
       <c r="K17" s="114"/>
@@ -4100,24 +4128,24 @@
       </c>
       <c r="AQ17" s="68"/>
       <c r="AS17" s="50" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
       <c r="AT17" s="44" t="e">
         <f>AS12/(AS10*PI()*($AM$11*25.4/2000)^2)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AU17" s="8" t="s">
+        <v>128</v>
+      </c>
+      <c r="AV17" s="50" t="s">
         <v>129</v>
-      </c>
-      <c r="AV17" s="50" t="s">
-        <v>130</v>
       </c>
       <c r="AW17" s="44" t="e">
         <f>AV13/(AS10*PI()*($AM$11*25.4/2000)^2)</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX17" s="8" t="s">
-        <v>129</v>
+        <v>128</v>
       </c>
     </row>
     <row r="18" spans="1:52" ht="45" customHeight="1" thickBot="1">
@@ -4177,24 +4205,24 @@
       </c>
       <c r="AQ18" s="69"/>
       <c r="AS18" s="51" t="s">
-        <v>131</v>
+        <v>130</v>
       </c>
       <c r="AT18" s="45" t="e">
         <f>AT17*PI()*($AM$11*25.4/2000)^2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AU18" s="46" t="s">
+        <v>131</v>
+      </c>
+      <c r="AV18" s="51" t="s">
         <v>132</v>
-      </c>
-      <c r="AV18" s="51" t="s">
-        <v>133</v>
       </c>
       <c r="AW18" s="45" t="e">
         <f>AW17*PI()*($AM$11*25.4/2000)^2</f>
         <v>#DIV/0!</v>
       </c>
       <c r="AX18" s="46" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="19" spans="1:52" ht="45" customHeight="1">
@@ -4366,7 +4394,7 @@
       </c>
       <c r="AM21" s="7"/>
       <c r="AN21" s="190" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="AO21" s="191"/>
       <c r="AP21" s="191"/>
@@ -4376,13 +4404,13 @@
       <c r="AT21" s="191"/>
       <c r="AU21" s="192"/>
       <c r="AV21" s="186" t="s">
+        <v>134</v>
+      </c>
+      <c r="AW21" s="188" t="s">
         <v>135</v>
       </c>
-      <c r="AW21" s="188" t="s">
+      <c r="AX21" s="181" t="s">
         <v>136</v>
-      </c>
-      <c r="AX21" s="181" t="s">
-        <v>137</v>
       </c>
       <c r="AY21" s="182"/>
     </row>
@@ -4442,42 +4470,42 @@
         <v/>
       </c>
       <c r="AM22" s="76" t="s">
+        <v>137</v>
+      </c>
+      <c r="AN22" s="35" t="s">
         <v>138</v>
       </c>
-      <c r="AN22" s="35" t="s">
+      <c r="AO22" s="36" t="s">
         <v>139</v>
       </c>
-      <c r="AO22" s="36" t="s">
+      <c r="AP22" s="36" t="s">
         <v>140</v>
       </c>
-      <c r="AP22" s="36" t="s">
+      <c r="AQ22" s="36" t="s">
         <v>141</v>
       </c>
-      <c r="AQ22" s="36" t="s">
+      <c r="AR22" s="36" t="s">
         <v>142</v>
       </c>
-      <c r="AR22" s="36" t="s">
+      <c r="AS22" s="64" t="s">
         <v>143</v>
       </c>
-      <c r="AS22" s="64" t="s">
+      <c r="AT22" s="36" t="s">
         <v>144</v>
       </c>
-      <c r="AT22" s="36" t="s">
+      <c r="AU22" s="62" t="s">
         <v>145</v>
-      </c>
-      <c r="AU22" s="62" t="s">
-        <v>146</v>
       </c>
       <c r="AV22" s="187"/>
       <c r="AW22" s="189"/>
       <c r="AX22" s="48" t="s">
+        <v>146</v>
+      </c>
+      <c r="AY22" s="39" t="s">
         <v>147</v>
       </c>
-      <c r="AY22" s="39" t="s">
+      <c r="AZ22" s="56" t="s">
         <v>148</v>
-      </c>
-      <c r="AZ22" s="56" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="23" spans="1:52" ht="45" customHeight="1">
@@ -5661,7 +5689,7 @@
         <v/>
       </c>
       <c r="AM34" s="1" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
       <c r="AO34" s="1">
         <f>SUM(AO23:AO33)+AN23-AT32</f>
@@ -5756,7 +5784,7 @@
         <v/>
       </c>
       <c r="AV35" s="37" t="s">
-        <v>151</v>
+        <v>150</v>
       </c>
       <c r="AW35" s="92" t="e">
         <f>AW17</f>
@@ -5819,7 +5847,7 @@
         <v/>
       </c>
       <c r="AV36" s="49" t="s">
-        <v>152</v>
+        <v>151</v>
       </c>
       <c r="AW36" s="60">
         <f>AM12</f>
@@ -8578,7 +8606,7 @@
     </row>
     <row r="85" spans="1:43" ht="45" customHeight="1">
       <c r="B85" s="266" t="s">
-        <v>153</v>
+        <v>152</v>
       </c>
       <c r="C85" s="266"/>
       <c r="D85" s="266"/>

--- a/plantillas/plantilla.xlsx
+++ b/plantillas/plantilla.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\00.- JEJ\01.- WORKS 2023\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{A52C23F2-CD2F-4607-AFA9-048949D5917D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{28A1004F-12DA-4BC3-9C16-F8B907BF8096}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="20370" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -668,7 +668,7 @@
       <family val="2"/>
     </font>
   </fonts>
-  <fills count="18">
+  <fills count="16">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -759,18 +759,6 @@
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FFFFFF00"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF92D050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
-    </fill>
   </fills>
   <borders count="68">
     <border>
@@ -1670,7 +1658,7 @@
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="9" fontId="2" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="279">
+  <cellXfs count="276">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -2215,15 +2203,6 @@
     <xf numFmtId="0" fontId="17" fillId="10" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
       <protection locked="0"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="16" borderId="1" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="16" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="1" fontId="13" fillId="17" borderId="12" xfId="2" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="166" fontId="4" fillId="4" borderId="2" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1" applyProtection="1">
       <alignment horizontal="center" vertical="center"/>
@@ -3143,8 +3122,8 @@
       <c r="L2" s="3"/>
       <c r="M2" s="3"/>
       <c r="N2" s="3"/>
-      <c r="O2" s="159"/>
-      <c r="P2" s="159"/>
+      <c r="O2" s="156"/>
+      <c r="P2" s="156"/>
       <c r="Q2" s="2"/>
       <c r="R2" s="2"/>
       <c r="S2" s="2"/>
@@ -3159,32 +3138,32 @@
       </c>
     </row>
     <row r="3" spans="2:51" ht="45" customHeight="1" thickBot="1">
-      <c r="B3" s="245"/>
-      <c r="C3" s="246"/>
-      <c r="D3" s="246"/>
-      <c r="E3" s="247"/>
-      <c r="F3" s="160" t="s">
+      <c r="B3" s="242"/>
+      <c r="C3" s="243"/>
+      <c r="D3" s="243"/>
+      <c r="E3" s="244"/>
+      <c r="F3" s="157" t="s">
         <v>3</v>
       </c>
-      <c r="G3" s="160"/>
-      <c r="H3" s="160"/>
-      <c r="I3" s="160"/>
-      <c r="J3" s="160"/>
-      <c r="K3" s="160"/>
-      <c r="L3" s="160"/>
-      <c r="M3" s="160"/>
-      <c r="N3" s="160"/>
-      <c r="O3" s="160"/>
-      <c r="P3" s="160"/>
-      <c r="Q3" s="160"/>
-      <c r="R3" s="160"/>
-      <c r="S3" s="160"/>
-      <c r="T3" s="160"/>
-      <c r="U3" s="160"/>
-      <c r="V3" s="160"/>
-      <c r="W3" s="160"/>
-      <c r="X3" s="160"/>
-      <c r="Y3" s="161"/>
+      <c r="G3" s="157"/>
+      <c r="H3" s="157"/>
+      <c r="I3" s="157"/>
+      <c r="J3" s="157"/>
+      <c r="K3" s="157"/>
+      <c r="L3" s="157"/>
+      <c r="M3" s="157"/>
+      <c r="N3" s="157"/>
+      <c r="O3" s="157"/>
+      <c r="P3" s="157"/>
+      <c r="Q3" s="157"/>
+      <c r="R3" s="157"/>
+      <c r="S3" s="157"/>
+      <c r="T3" s="157"/>
+      <c r="U3" s="157"/>
+      <c r="V3" s="157"/>
+      <c r="W3" s="157"/>
+      <c r="X3" s="157"/>
+      <c r="Y3" s="158"/>
       <c r="AL3" s="17" t="s">
         <v>4</v>
       </c>
@@ -3198,36 +3177,36 @@
       </c>
     </row>
     <row r="4" spans="2:51" ht="45" customHeight="1">
-      <c r="B4" s="248"/>
-      <c r="C4" s="249"/>
-      <c r="D4" s="249"/>
-      <c r="E4" s="250"/>
-      <c r="F4" s="162" t="s">
+      <c r="B4" s="245"/>
+      <c r="C4" s="246"/>
+      <c r="D4" s="246"/>
+      <c r="E4" s="247"/>
+      <c r="F4" s="159" t="s">
         <v>5</v>
       </c>
-      <c r="G4" s="162"/>
-      <c r="H4" s="162"/>
-      <c r="I4" s="162"/>
-      <c r="J4" s="162"/>
-      <c r="K4" s="162"/>
-      <c r="L4" s="162"/>
-      <c r="M4" s="162"/>
-      <c r="N4" s="162"/>
-      <c r="O4" s="162"/>
-      <c r="P4" s="162"/>
-      <c r="Q4" s="162"/>
-      <c r="R4" s="162"/>
-      <c r="S4" s="162"/>
-      <c r="T4" s="162"/>
-      <c r="U4" s="162"/>
-      <c r="V4" s="162"/>
-      <c r="W4" s="162"/>
-      <c r="X4" s="162"/>
-      <c r="Y4" s="163"/>
-      <c r="AA4" s="223" t="s">
+      <c r="G4" s="159"/>
+      <c r="H4" s="159"/>
+      <c r="I4" s="159"/>
+      <c r="J4" s="159"/>
+      <c r="K4" s="159"/>
+      <c r="L4" s="159"/>
+      <c r="M4" s="159"/>
+      <c r="N4" s="159"/>
+      <c r="O4" s="159"/>
+      <c r="P4" s="159"/>
+      <c r="Q4" s="159"/>
+      <c r="R4" s="159"/>
+      <c r="S4" s="159"/>
+      <c r="T4" s="159"/>
+      <c r="U4" s="159"/>
+      <c r="V4" s="159"/>
+      <c r="W4" s="159"/>
+      <c r="X4" s="159"/>
+      <c r="Y4" s="160"/>
+      <c r="AA4" s="220" t="s">
         <v>6</v>
       </c>
-      <c r="AB4" s="224"/>
+      <c r="AB4" s="221"/>
       <c r="AL4" s="17" t="s">
         <v>7</v>
       </c>
@@ -3254,32 +3233,32 @@
       </c>
     </row>
     <row r="5" spans="2:51" ht="45" customHeight="1" thickBot="1">
-      <c r="B5" s="248"/>
-      <c r="C5" s="249"/>
-      <c r="D5" s="249"/>
-      <c r="E5" s="250"/>
-      <c r="F5" s="162" t="s">
+      <c r="B5" s="245"/>
+      <c r="C5" s="246"/>
+      <c r="D5" s="246"/>
+      <c r="E5" s="247"/>
+      <c r="F5" s="159" t="s">
         <v>10</v>
       </c>
-      <c r="G5" s="162"/>
-      <c r="H5" s="162"/>
-      <c r="I5" s="162"/>
-      <c r="J5" s="162"/>
-      <c r="K5" s="162"/>
-      <c r="L5" s="162"/>
-      <c r="M5" s="162"/>
-      <c r="N5" s="162"/>
-      <c r="O5" s="162"/>
-      <c r="P5" s="162"/>
-      <c r="Q5" s="162"/>
-      <c r="R5" s="162"/>
-      <c r="S5" s="162"/>
-      <c r="T5" s="162"/>
-      <c r="U5" s="162"/>
-      <c r="V5" s="162"/>
-      <c r="W5" s="162"/>
-      <c r="X5" s="162"/>
-      <c r="Y5" s="163"/>
+      <c r="G5" s="159"/>
+      <c r="H5" s="159"/>
+      <c r="I5" s="159"/>
+      <c r="J5" s="159"/>
+      <c r="K5" s="159"/>
+      <c r="L5" s="159"/>
+      <c r="M5" s="159"/>
+      <c r="N5" s="159"/>
+      <c r="O5" s="159"/>
+      <c r="P5" s="159"/>
+      <c r="Q5" s="159"/>
+      <c r="R5" s="159"/>
+      <c r="S5" s="159"/>
+      <c r="T5" s="159"/>
+      <c r="U5" s="159"/>
+      <c r="V5" s="159"/>
+      <c r="W5" s="159"/>
+      <c r="X5" s="159"/>
+      <c r="Y5" s="160"/>
       <c r="AA5" s="98" t="s">
         <v>11</v>
       </c>
@@ -3312,39 +3291,39 @@
       </c>
     </row>
     <row r="6" spans="2:51" ht="45" customHeight="1" thickBot="1">
-      <c r="B6" s="157" t="s">
+      <c r="B6" s="154" t="s">
         <v>16</v>
       </c>
-      <c r="C6" s="158"/>
-      <c r="D6" s="155"/>
-      <c r="E6" s="156"/>
-      <c r="F6" s="157" t="s">
+      <c r="C6" s="155"/>
+      <c r="D6" s="152"/>
+      <c r="E6" s="153"/>
+      <c r="F6" s="154" t="s">
         <v>17</v>
       </c>
-      <c r="G6" s="158"/>
+      <c r="G6" s="155"/>
       <c r="H6" s="132"/>
-      <c r="I6" s="157" t="s">
+      <c r="I6" s="154" t="s">
         <v>18</v>
       </c>
-      <c r="J6" s="158"/>
-      <c r="K6" s="170"/>
-      <c r="L6" s="171"/>
+      <c r="J6" s="155"/>
+      <c r="K6" s="167"/>
+      <c r="L6" s="168"/>
       <c r="M6" s="126" t="s">
         <v>19</v>
       </c>
-      <c r="N6" s="175"/>
-      <c r="O6" s="176"/>
-      <c r="P6" s="242" t="s">
+      <c r="N6" s="172"/>
+      <c r="O6" s="173"/>
+      <c r="P6" s="239" t="s">
         <v>20</v>
       </c>
-      <c r="Q6" s="243"/>
-      <c r="R6" s="243"/>
-      <c r="S6" s="243"/>
-      <c r="T6" s="243"/>
-      <c r="U6" s="243"/>
-      <c r="V6" s="243"/>
-      <c r="W6" s="243"/>
-      <c r="X6" s="244"/>
+      <c r="Q6" s="240"/>
+      <c r="R6" s="240"/>
+      <c r="S6" s="240"/>
+      <c r="T6" s="240"/>
+      <c r="U6" s="240"/>
+      <c r="V6" s="240"/>
+      <c r="W6" s="240"/>
+      <c r="X6" s="241"/>
       <c r="Y6" s="100" t="s">
         <v>21</v>
       </c>
@@ -3357,37 +3336,37 @@
       </c>
     </row>
     <row r="7" spans="2:51" ht="45" customHeight="1" thickBot="1">
-      <c r="B7" s="150" t="s">
+      <c r="B7" s="147" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="151"/>
-      <c r="D7" s="151"/>
-      <c r="E7" s="152"/>
-      <c r="F7" s="164" t="s">
+      <c r="C7" s="148"/>
+      <c r="D7" s="148"/>
+      <c r="E7" s="149"/>
+      <c r="F7" s="161" t="s">
         <v>24</v>
       </c>
-      <c r="G7" s="165"/>
+      <c r="G7" s="162"/>
       <c r="H7" s="133"/>
-      <c r="I7" s="166" t="s">
+      <c r="I7" s="163" t="s">
         <v>25</v>
       </c>
-      <c r="J7" s="167"/>
-      <c r="K7" s="168"/>
-      <c r="L7" s="169"/>
-      <c r="M7" s="172" t="s">
+      <c r="J7" s="164"/>
+      <c r="K7" s="165"/>
+      <c r="L7" s="166"/>
+      <c r="M7" s="169" t="s">
         <v>26</v>
       </c>
-      <c r="N7" s="226"/>
-      <c r="O7" s="228"/>
-      <c r="P7" s="236"/>
-      <c r="Q7" s="237"/>
-      <c r="R7" s="237"/>
-      <c r="S7" s="237"/>
-      <c r="T7" s="237"/>
-      <c r="U7" s="237"/>
-      <c r="V7" s="237"/>
-      <c r="W7" s="237"/>
-      <c r="X7" s="238"/>
+      <c r="N7" s="223"/>
+      <c r="O7" s="225"/>
+      <c r="P7" s="233"/>
+      <c r="Q7" s="234"/>
+      <c r="R7" s="234"/>
+      <c r="S7" s="234"/>
+      <c r="T7" s="234"/>
+      <c r="U7" s="234"/>
+      <c r="V7" s="234"/>
+      <c r="W7" s="234"/>
+      <c r="X7" s="235"/>
       <c r="Y7" s="101"/>
       <c r="AA7" s="94" t="s">
         <v>27</v>
@@ -3398,38 +3377,38 @@
       </c>
     </row>
     <row r="8" spans="2:51" ht="45" customHeight="1">
-      <c r="B8" s="150" t="s">
+      <c r="B8" s="147" t="s">
         <v>28</v>
       </c>
-      <c r="C8" s="151"/>
-      <c r="D8" s="151"/>
-      <c r="E8" s="152"/>
-      <c r="F8" s="173" t="s">
+      <c r="C8" s="148"/>
+      <c r="D8" s="148"/>
+      <c r="E8" s="149"/>
+      <c r="F8" s="170" t="s">
         <v>29</v>
       </c>
-      <c r="G8" s="174"/>
+      <c r="G8" s="171"/>
       <c r="H8" s="134"/>
-      <c r="I8" s="177" t="s">
+      <c r="I8" s="174" t="s">
         <v>30</v>
       </c>
-      <c r="J8" s="178"/>
-      <c r="K8" s="179">
+      <c r="J8" s="175"/>
+      <c r="K8" s="176">
         <f>IF(AO34=0,"",AO34)</f>
         <v>124</v>
       </c>
-      <c r="L8" s="180"/>
-      <c r="M8" s="172"/>
-      <c r="N8" s="227"/>
-      <c r="O8" s="229"/>
-      <c r="P8" s="233"/>
-      <c r="Q8" s="234"/>
-      <c r="R8" s="234"/>
-      <c r="S8" s="234"/>
-      <c r="T8" s="234"/>
-      <c r="U8" s="234"/>
-      <c r="V8" s="234"/>
-      <c r="W8" s="234"/>
-      <c r="X8" s="235"/>
+      <c r="L8" s="177"/>
+      <c r="M8" s="169"/>
+      <c r="N8" s="224"/>
+      <c r="O8" s="226"/>
+      <c r="P8" s="230"/>
+      <c r="Q8" s="231"/>
+      <c r="R8" s="231"/>
+      <c r="S8" s="231"/>
+      <c r="T8" s="231"/>
+      <c r="U8" s="231"/>
+      <c r="V8" s="231"/>
+      <c r="W8" s="231"/>
+      <c r="X8" s="232"/>
       <c r="Y8" s="101"/>
       <c r="AA8" s="94" t="s">
         <v>31</v>
@@ -3440,40 +3419,40 @@
       </c>
     </row>
     <row r="9" spans="2:51" ht="45" customHeight="1" thickBot="1">
-      <c r="B9" s="150" t="s">
+      <c r="B9" s="147" t="s">
         <v>32</v>
       </c>
-      <c r="C9" s="151"/>
-      <c r="D9" s="151"/>
-      <c r="E9" s="258"/>
-      <c r="F9" s="153" t="s">
+      <c r="C9" s="148"/>
+      <c r="D9" s="148"/>
+      <c r="E9" s="255"/>
+      <c r="F9" s="150" t="s">
         <v>33</v>
       </c>
-      <c r="G9" s="154"/>
+      <c r="G9" s="151"/>
       <c r="H9" s="135"/>
-      <c r="I9" s="251" t="s">
+      <c r="I9" s="248" t="s">
         <v>34</v>
       </c>
-      <c r="J9" s="252"/>
-      <c r="K9" s="277">
+      <c r="J9" s="249"/>
+      <c r="K9" s="274">
         <f>IF(AP34=0,"",AP34)</f>
         <v>2397.2800000000002</v>
       </c>
-      <c r="L9" s="278"/>
+      <c r="L9" s="275"/>
       <c r="M9" s="104" t="s">
         <v>35</v>
       </c>
-      <c r="N9" s="256"/>
-      <c r="O9" s="257"/>
-      <c r="P9" s="233"/>
-      <c r="Q9" s="234"/>
-      <c r="R9" s="234"/>
-      <c r="S9" s="234"/>
-      <c r="T9" s="234"/>
-      <c r="U9" s="234"/>
-      <c r="V9" s="234"/>
-      <c r="W9" s="234"/>
-      <c r="X9" s="235"/>
+      <c r="N9" s="253"/>
+      <c r="O9" s="254"/>
+      <c r="P9" s="230"/>
+      <c r="Q9" s="231"/>
+      <c r="R9" s="231"/>
+      <c r="S9" s="231"/>
+      <c r="T9" s="231"/>
+      <c r="U9" s="231"/>
+      <c r="V9" s="231"/>
+      <c r="W9" s="231"/>
+      <c r="X9" s="232"/>
       <c r="Y9" s="101"/>
       <c r="AA9" s="94" t="s">
         <v>36</v>
@@ -3484,21 +3463,21 @@
       </c>
     </row>
     <row r="10" spans="2:51" ht="45" customHeight="1">
-      <c r="B10" s="150" t="s">
+      <c r="B10" s="147" t="s">
         <v>37</v>
       </c>
-      <c r="C10" s="151"/>
-      <c r="D10" s="151"/>
-      <c r="E10" s="258"/>
-      <c r="F10" s="153" t="s">
+      <c r="C10" s="148"/>
+      <c r="D10" s="148"/>
+      <c r="E10" s="255"/>
+      <c r="F10" s="150" t="s">
         <v>38</v>
       </c>
-      <c r="G10" s="154"/>
+      <c r="G10" s="151"/>
       <c r="H10" s="135"/>
-      <c r="I10" s="251" t="s">
+      <c r="I10" s="248" t="s">
         <v>39</v>
       </c>
-      <c r="J10" s="252"/>
+      <c r="J10" s="249"/>
       <c r="K10" s="105" t="str">
         <f>IF($AW$34=0,"",9/$AW$34)</f>
         <v/>
@@ -3507,20 +3486,20 @@
         <f>IF(K10="","",IF(K10&gt;=K11,IF(K10&lt;=L11,"Ok","Fuera de Rango Alto"),"Fuera de Rango Bajo"))</f>
         <v/>
       </c>
-      <c r="M10" s="267" t="s">
+      <c r="M10" s="264" t="s">
         <v>40</v>
       </c>
-      <c r="N10" s="202"/>
+      <c r="N10" s="199"/>
       <c r="O10" s="127"/>
-      <c r="P10" s="230"/>
-      <c r="Q10" s="231"/>
-      <c r="R10" s="231"/>
-      <c r="S10" s="231"/>
-      <c r="T10" s="231"/>
-      <c r="U10" s="231"/>
-      <c r="V10" s="231"/>
-      <c r="W10" s="231"/>
-      <c r="X10" s="232"/>
+      <c r="P10" s="227"/>
+      <c r="Q10" s="228"/>
+      <c r="R10" s="228"/>
+      <c r="S10" s="228"/>
+      <c r="T10" s="228"/>
+      <c r="U10" s="228"/>
+      <c r="V10" s="228"/>
+      <c r="W10" s="228"/>
+      <c r="X10" s="229"/>
       <c r="Y10" s="102"/>
       <c r="AA10" s="94" t="s">
         <v>41</v>
@@ -3550,21 +3529,21 @@
       </c>
     </row>
     <row r="11" spans="2:51" ht="45" customHeight="1" thickBot="1">
-      <c r="B11" s="255" t="s">
+      <c r="B11" s="252" t="s">
         <v>46</v>
       </c>
-      <c r="C11" s="216"/>
-      <c r="D11" s="216"/>
-      <c r="E11" s="259"/>
-      <c r="F11" s="275" t="s">
+      <c r="C11" s="213"/>
+      <c r="D11" s="213"/>
+      <c r="E11" s="256"/>
+      <c r="F11" s="272" t="s">
         <v>47</v>
       </c>
-      <c r="G11" s="276"/>
+      <c r="G11" s="273"/>
       <c r="H11" s="136"/>
-      <c r="I11" s="211" t="s">
+      <c r="I11" s="208" t="s">
         <v>48</v>
       </c>
-      <c r="J11" s="212"/>
+      <c r="J11" s="209"/>
       <c r="K11" s="108" t="str">
         <f>IF(H14="","",AQ4*PI()*(H14*25.4/2000)^2)</f>
         <v/>
@@ -3573,22 +3552,22 @@
         <f>IF(H14="","",AQ5*PI()*(H14*25.4/2000)^2)</f>
         <v/>
       </c>
-      <c r="M11" s="172" t="s">
+      <c r="M11" s="169" t="s">
         <v>49</v>
       </c>
-      <c r="N11" s="204"/>
+      <c r="N11" s="201"/>
       <c r="O11" s="128"/>
-      <c r="P11" s="239" t="s">
+      <c r="P11" s="236" t="s">
         <v>50</v>
       </c>
-      <c r="Q11" s="240"/>
-      <c r="R11" s="240"/>
-      <c r="S11" s="240"/>
-      <c r="T11" s="240"/>
-      <c r="U11" s="240"/>
-      <c r="V11" s="240"/>
-      <c r="W11" s="240"/>
-      <c r="X11" s="241"/>
+      <c r="Q11" s="237"/>
+      <c r="R11" s="237"/>
+      <c r="S11" s="237"/>
+      <c r="T11" s="237"/>
+      <c r="U11" s="237"/>
+      <c r="V11" s="237"/>
+      <c r="W11" s="237"/>
+      <c r="X11" s="238"/>
       <c r="Y11" s="100" t="s">
         <v>21</v>
       </c>
@@ -3609,36 +3588,36 @@
       <c r="AN11" s="18" t="s">
         <v>53</v>
       </c>
-      <c r="AR11" s="183" t="s">
+      <c r="AR11" s="180" t="s">
         <v>54</v>
       </c>
-      <c r="AS11" s="184"/>
-      <c r="AT11" s="185"/>
-      <c r="AU11" s="183" t="s">
+      <c r="AS11" s="181"/>
+      <c r="AT11" s="182"/>
+      <c r="AU11" s="180" t="s">
         <v>55</v>
       </c>
-      <c r="AV11" s="184"/>
-      <c r="AW11" s="185"/>
+      <c r="AV11" s="181"/>
+      <c r="AW11" s="182"/>
     </row>
     <row r="12" spans="2:51" ht="45" customHeight="1">
-      <c r="B12" s="253" t="s">
+      <c r="B12" s="250" t="s">
         <v>56</v>
       </c>
-      <c r="C12" s="254"/>
-      <c r="D12" s="260"/>
-      <c r="E12" s="261"/>
-      <c r="F12" s="273" t="s">
+      <c r="C12" s="251"/>
+      <c r="D12" s="257"/>
+      <c r="E12" s="258"/>
+      <c r="F12" s="270" t="s">
         <v>57</v>
       </c>
-      <c r="G12" s="274"/>
+      <c r="G12" s="271"/>
       <c r="H12" s="86" t="str">
         <f>IF(H11="","",IF(H8="","",H11-H8))</f>
         <v/>
       </c>
-      <c r="I12" s="213" t="s">
+      <c r="I12" s="210" t="s">
         <v>58</v>
       </c>
-      <c r="J12" s="214"/>
+      <c r="J12" s="211"/>
       <c r="K12" s="107" t="str">
         <f>IF(SUM(F17:F83)=0,"",(SUM(F17:F83)-SUM(G17:G83))*K11)</f>
         <v/>
@@ -3647,20 +3626,20 @@
         <f>IF(SUM(G17:G83)=0,"",(SUM(G17:G83)-SUM(H17:H83))*L11)</f>
         <v/>
       </c>
-      <c r="M12" s="268" t="s">
+      <c r="M12" s="265" t="s">
         <v>59</v>
       </c>
-      <c r="N12" s="269"/>
+      <c r="N12" s="266"/>
       <c r="O12" s="129"/>
-      <c r="P12" s="236"/>
-      <c r="Q12" s="237"/>
-      <c r="R12" s="237"/>
-      <c r="S12" s="237"/>
-      <c r="T12" s="237"/>
-      <c r="U12" s="237"/>
-      <c r="V12" s="237"/>
-      <c r="W12" s="237"/>
-      <c r="X12" s="238"/>
+      <c r="P12" s="233"/>
+      <c r="Q12" s="234"/>
+      <c r="R12" s="234"/>
+      <c r="S12" s="234"/>
+      <c r="T12" s="234"/>
+      <c r="U12" s="234"/>
+      <c r="V12" s="234"/>
+      <c r="W12" s="234"/>
+      <c r="X12" s="235"/>
       <c r="Y12" s="101"/>
       <c r="AL12" s="17" t="s">
         <v>60</v>
@@ -3693,40 +3672,40 @@
       </c>
     </row>
     <row r="13" spans="2:51" ht="45" customHeight="1">
-      <c r="B13" s="264" t="s">
+      <c r="B13" s="261" t="s">
         <v>65</v>
       </c>
-      <c r="C13" s="265"/>
-      <c r="D13" s="262"/>
-      <c r="E13" s="263"/>
-      <c r="F13" s="272" t="s">
+      <c r="C13" s="262"/>
+      <c r="D13" s="259"/>
+      <c r="E13" s="260"/>
+      <c r="F13" s="269" t="s">
         <v>66</v>
       </c>
-      <c r="G13" s="215"/>
+      <c r="G13" s="212"/>
       <c r="H13" s="87" t="str">
         <f>IF(H10="","",IF(H9="","",H10-H9))</f>
         <v/>
       </c>
-      <c r="I13" s="209" t="s">
+      <c r="I13" s="206" t="s">
         <v>67</v>
       </c>
-      <c r="J13" s="210"/>
-      <c r="K13" s="270"/>
-      <c r="L13" s="271"/>
-      <c r="M13" s="202" t="s">
+      <c r="J13" s="207"/>
+      <c r="K13" s="267"/>
+      <c r="L13" s="268"/>
+      <c r="M13" s="199" t="s">
         <v>68</v>
       </c>
-      <c r="N13" s="203"/>
+      <c r="N13" s="200"/>
       <c r="O13" s="130"/>
-      <c r="P13" s="233"/>
-      <c r="Q13" s="234"/>
-      <c r="R13" s="234"/>
-      <c r="S13" s="234"/>
-      <c r="T13" s="234"/>
-      <c r="U13" s="234"/>
-      <c r="V13" s="234"/>
-      <c r="W13" s="234"/>
-      <c r="X13" s="235"/>
+      <c r="P13" s="230"/>
+      <c r="Q13" s="231"/>
+      <c r="R13" s="231"/>
+      <c r="S13" s="231"/>
+      <c r="T13" s="231"/>
+      <c r="U13" s="231"/>
+      <c r="V13" s="231"/>
+      <c r="W13" s="231"/>
+      <c r="X13" s="232"/>
       <c r="Y13" s="115"/>
       <c r="AL13" s="17" t="s">
         <v>69</v>
@@ -3766,51 +3745,51 @@
       </c>
     </row>
     <row r="14" spans="2:51" ht="45" customHeight="1" thickBot="1">
-      <c r="B14" s="157" t="s">
+      <c r="B14" s="154" t="s">
         <v>74</v>
       </c>
-      <c r="C14" s="158"/>
-      <c r="D14" s="270"/>
-      <c r="E14" s="271"/>
-      <c r="F14" s="195" t="s">
+      <c r="C14" s="155"/>
+      <c r="D14" s="267"/>
+      <c r="E14" s="268"/>
+      <c r="F14" s="192" t="s">
         <v>75</v>
       </c>
-      <c r="G14" s="196"/>
+      <c r="G14" s="193"/>
       <c r="H14" s="85"/>
-      <c r="I14" s="199" t="s">
+      <c r="I14" s="196" t="s">
         <v>76</v>
       </c>
-      <c r="J14" s="200"/>
-      <c r="K14" s="220"/>
-      <c r="L14" s="221"/>
-      <c r="M14" s="154" t="s">
+      <c r="J14" s="197"/>
+      <c r="K14" s="217"/>
+      <c r="L14" s="218"/>
+      <c r="M14" s="151" t="s">
         <v>77</v>
       </c>
-      <c r="N14" s="201"/>
+      <c r="N14" s="198"/>
       <c r="O14" s="131"/>
-      <c r="P14" s="233"/>
-      <c r="Q14" s="234"/>
-      <c r="R14" s="234"/>
-      <c r="S14" s="234"/>
-      <c r="T14" s="234"/>
-      <c r="U14" s="234"/>
-      <c r="V14" s="234"/>
-      <c r="W14" s="234"/>
-      <c r="X14" s="235"/>
+      <c r="P14" s="230"/>
+      <c r="Q14" s="231"/>
+      <c r="R14" s="231"/>
+      <c r="S14" s="231"/>
+      <c r="T14" s="231"/>
+      <c r="U14" s="231"/>
+      <c r="V14" s="231"/>
+      <c r="W14" s="231"/>
+      <c r="X14" s="232"/>
       <c r="Y14" s="101"/>
-      <c r="Z14" s="217" t="s">
+      <c r="Z14" s="214" t="s">
         <v>78</v>
       </c>
-      <c r="AA14" s="218"/>
-      <c r="AB14" s="218"/>
-      <c r="AC14" s="218"/>
-      <c r="AD14" s="218"/>
-      <c r="AE14" s="218"/>
-      <c r="AF14" s="218"/>
-      <c r="AG14" s="218"/>
-      <c r="AH14" s="218"/>
-      <c r="AI14" s="218"/>
-      <c r="AJ14" s="219"/>
+      <c r="AA14" s="215"/>
+      <c r="AB14" s="215"/>
+      <c r="AC14" s="215"/>
+      <c r="AD14" s="215"/>
+      <c r="AE14" s="215"/>
+      <c r="AF14" s="215"/>
+      <c r="AG14" s="215"/>
+      <c r="AH14" s="215"/>
+      <c r="AI14" s="215"/>
+      <c r="AJ14" s="216"/>
       <c r="AL14" s="17" t="s">
         <v>79</v>
       </c>
@@ -3846,64 +3825,64 @@
       </c>
     </row>
     <row r="15" spans="2:51" ht="54">
-      <c r="B15" s="164" t="s">
+      <c r="B15" s="161" t="s">
         <v>84</v>
       </c>
-      <c r="C15" s="165"/>
-      <c r="D15" s="193"/>
-      <c r="E15" s="194"/>
-      <c r="F15" s="207" t="s">
+      <c r="C15" s="162"/>
+      <c r="D15" s="190"/>
+      <c r="E15" s="191"/>
+      <c r="F15" s="204" t="s">
         <v>85</v>
       </c>
-      <c r="G15" s="208"/>
+      <c r="G15" s="205"/>
       <c r="H15" s="125"/>
-      <c r="I15" s="197" t="s">
+      <c r="I15" s="194" t="s">
         <v>86</v>
       </c>
-      <c r="J15" s="198"/>
-      <c r="K15" s="193"/>
-      <c r="L15" s="194"/>
-      <c r="M15" s="215" t="s">
+      <c r="J15" s="195"/>
+      <c r="K15" s="190"/>
+      <c r="L15" s="191"/>
+      <c r="M15" s="212" t="s">
         <v>87</v>
       </c>
-      <c r="N15" s="216"/>
+      <c r="N15" s="213"/>
       <c r="O15" s="87" t="str">
         <f>IF(O14="","",IF(O13="","",O14-O13))</f>
         <v/>
       </c>
-      <c r="P15" s="230"/>
-      <c r="Q15" s="231"/>
-      <c r="R15" s="231"/>
-      <c r="S15" s="231"/>
-      <c r="T15" s="231"/>
-      <c r="U15" s="231"/>
-      <c r="V15" s="231"/>
-      <c r="W15" s="231"/>
-      <c r="X15" s="232"/>
+      <c r="P15" s="227"/>
+      <c r="Q15" s="228"/>
+      <c r="R15" s="228"/>
+      <c r="S15" s="228"/>
+      <c r="T15" s="228"/>
+      <c r="U15" s="228"/>
+      <c r="V15" s="228"/>
+      <c r="W15" s="228"/>
+      <c r="X15" s="229"/>
       <c r="Y15" s="103"/>
       <c r="Z15" s="140" t="s">
         <v>88</v>
       </c>
-      <c r="AA15" s="206" t="s">
+      <c r="AA15" s="203" t="s">
         <v>89</v>
       </c>
-      <c r="AB15" s="206"/>
-      <c r="AC15" s="205" t="s">
+      <c r="AB15" s="203"/>
+      <c r="AC15" s="202" t="s">
         <v>90</v>
       </c>
-      <c r="AD15" s="205"/>
-      <c r="AE15" s="206" t="s">
+      <c r="AD15" s="202"/>
+      <c r="AE15" s="203" t="s">
         <v>91</v>
       </c>
-      <c r="AF15" s="206"/>
-      <c r="AG15" s="205" t="s">
+      <c r="AF15" s="203"/>
+      <c r="AG15" s="202" t="s">
         <v>92</v>
       </c>
-      <c r="AH15" s="205"/>
-      <c r="AI15" s="206" t="s">
+      <c r="AH15" s="202"/>
+      <c r="AI15" s="203" t="s">
         <v>93</v>
       </c>
-      <c r="AJ15" s="225"/>
+      <c r="AJ15" s="222"/>
       <c r="AL15" s="19" t="s">
         <v>94</v>
       </c>
@@ -4072,7 +4051,7 @@
       <c r="A17" s="1">
         <v>1</v>
       </c>
-      <c r="B17" s="148"/>
+      <c r="B17" s="110"/>
       <c r="C17" s="111"/>
       <c r="D17" s="112"/>
       <c r="E17" s="112"/>
@@ -4285,7 +4264,7 @@
       <c r="A20" s="1">
         <v>4</v>
       </c>
-      <c r="B20" s="148"/>
+      <c r="B20" s="110"/>
       <c r="C20" s="111"/>
       <c r="D20" s="112"/>
       <c r="E20" s="112"/>
@@ -4393,26 +4372,26 @@
         <v/>
       </c>
       <c r="AM21" s="7"/>
-      <c r="AN21" s="190" t="s">
+      <c r="AN21" s="187" t="s">
         <v>133</v>
       </c>
-      <c r="AO21" s="191"/>
-      <c r="AP21" s="191"/>
-      <c r="AQ21" s="191"/>
-      <c r="AR21" s="191"/>
-      <c r="AS21" s="191"/>
-      <c r="AT21" s="191"/>
-      <c r="AU21" s="192"/>
-      <c r="AV21" s="186" t="s">
+      <c r="AO21" s="188"/>
+      <c r="AP21" s="188"/>
+      <c r="AQ21" s="188"/>
+      <c r="AR21" s="188"/>
+      <c r="AS21" s="188"/>
+      <c r="AT21" s="188"/>
+      <c r="AU21" s="189"/>
+      <c r="AV21" s="183" t="s">
         <v>134</v>
       </c>
-      <c r="AW21" s="188" t="s">
+      <c r="AW21" s="185" t="s">
         <v>135</v>
       </c>
-      <c r="AX21" s="181" t="s">
+      <c r="AX21" s="178" t="s">
         <v>136</v>
       </c>
-      <c r="AY21" s="182"/>
+      <c r="AY21" s="179"/>
     </row>
     <row r="22" spans="1:52" ht="45" customHeight="1">
       <c r="A22" s="1">
@@ -4496,8 +4475,8 @@
       <c r="AU22" s="62" t="s">
         <v>145</v>
       </c>
-      <c r="AV22" s="187"/>
-      <c r="AW22" s="189"/>
+      <c r="AV22" s="184"/>
+      <c r="AW22" s="186"/>
       <c r="AX22" s="48" t="s">
         <v>146</v>
       </c>
@@ -4512,7 +4491,7 @@
       <c r="A23" s="1">
         <v>7</v>
       </c>
-      <c r="B23" s="148"/>
+      <c r="B23" s="110"/>
       <c r="C23" s="111"/>
       <c r="D23" s="112"/>
       <c r="E23" s="112"/>
@@ -4882,7 +4861,7 @@
       <c r="AN26" s="17">
         <v>16</v>
       </c>
-      <c r="AO26" s="149">
+      <c r="AO26" s="146">
         <v>16</v>
       </c>
       <c r="AP26" s="4">
@@ -5137,7 +5116,7 @@
       <c r="A29" s="1">
         <v>13</v>
       </c>
-      <c r="B29" s="148"/>
+      <c r="B29" s="110"/>
       <c r="C29" s="111"/>
       <c r="D29" s="112"/>
       <c r="E29" s="112"/>
@@ -5241,7 +5220,7 @@
       <c r="A30" s="1">
         <v>15</v>
       </c>
-      <c r="B30" s="148"/>
+      <c r="B30" s="110"/>
       <c r="C30" s="111"/>
       <c r="D30" s="112"/>
       <c r="E30" s="112"/>
@@ -5858,7 +5837,7 @@
       <c r="A37" s="1">
         <v>22</v>
       </c>
-      <c r="B37" s="148"/>
+      <c r="B37" s="110"/>
       <c r="C37" s="111"/>
       <c r="D37" s="112"/>
       <c r="E37" s="112"/>
@@ -5970,7 +5949,7 @@
       <c r="A39" s="1">
         <v>24</v>
       </c>
-      <c r="B39" s="148"/>
+      <c r="B39" s="110"/>
       <c r="C39" s="111"/>
       <c r="D39" s="112"/>
       <c r="E39" s="112"/>
@@ -6418,7 +6397,7 @@
       <c r="A47" s="1">
         <v>32</v>
       </c>
-      <c r="B47" s="148"/>
+      <c r="B47" s="110"/>
       <c r="C47" s="111"/>
       <c r="D47" s="112"/>
       <c r="E47" s="112"/>
@@ -6922,7 +6901,7 @@
       <c r="A56" s="1">
         <v>41</v>
       </c>
-      <c r="B56" s="148"/>
+      <c r="B56" s="110"/>
       <c r="C56" s="111"/>
       <c r="D56" s="112"/>
       <c r="E56" s="112"/>
@@ -7148,8 +7127,8 @@
       <c r="A60" s="1">
         <v>45</v>
       </c>
-      <c r="B60" s="147"/>
-      <c r="C60" s="146"/>
+      <c r="B60" s="110"/>
+      <c r="C60" s="111"/>
       <c r="D60" s="112"/>
       <c r="E60" s="112"/>
       <c r="F60" s="112"/>
@@ -8605,526 +8584,526 @@
       <c r="Y84" s="11"/>
     </row>
     <row r="85" spans="1:43" ht="45" customHeight="1">
-      <c r="B85" s="266" t="s">
+      <c r="B85" s="263" t="s">
         <v>152</v>
       </c>
-      <c r="C85" s="266"/>
-      <c r="D85" s="266"/>
-      <c r="E85" s="266"/>
-      <c r="F85" s="266"/>
-      <c r="G85" s="266"/>
-      <c r="H85" s="266"/>
-      <c r="I85" s="266"/>
-      <c r="J85" s="266"/>
-      <c r="K85" s="266"/>
-      <c r="L85" s="266"/>
-      <c r="M85" s="266"/>
-      <c r="N85" s="266"/>
-      <c r="O85" s="266"/>
-      <c r="P85" s="266"/>
-      <c r="Q85" s="266"/>
-      <c r="R85" s="266"/>
-      <c r="S85" s="266"/>
-      <c r="T85" s="266"/>
-      <c r="U85" s="266"/>
-      <c r="V85" s="266"/>
-      <c r="W85" s="266"/>
-      <c r="X85" s="266"/>
-      <c r="Y85" s="266"/>
+      <c r="C85" s="263"/>
+      <c r="D85" s="263"/>
+      <c r="E85" s="263"/>
+      <c r="F85" s="263"/>
+      <c r="G85" s="263"/>
+      <c r="H85" s="263"/>
+      <c r="I85" s="263"/>
+      <c r="J85" s="263"/>
+      <c r="K85" s="263"/>
+      <c r="L85" s="263"/>
+      <c r="M85" s="263"/>
+      <c r="N85" s="263"/>
+      <c r="O85" s="263"/>
+      <c r="P85" s="263"/>
+      <c r="Q85" s="263"/>
+      <c r="R85" s="263"/>
+      <c r="S85" s="263"/>
+      <c r="T85" s="263"/>
+      <c r="U85" s="263"/>
+      <c r="V85" s="263"/>
+      <c r="W85" s="263"/>
+      <c r="X85" s="263"/>
+      <c r="Y85" s="263"/>
     </row>
     <row r="86" spans="1:43" ht="45" customHeight="1">
-      <c r="B86" s="222"/>
-      <c r="C86" s="222"/>
-      <c r="D86" s="222"/>
-      <c r="E86" s="222"/>
-      <c r="F86" s="222"/>
-      <c r="G86" s="222"/>
-      <c r="H86" s="222"/>
-      <c r="I86" s="222"/>
-      <c r="J86" s="222"/>
-      <c r="K86" s="222"/>
-      <c r="L86" s="222"/>
-      <c r="M86" s="222"/>
-      <c r="N86" s="222"/>
-      <c r="O86" s="222"/>
-      <c r="P86" s="222"/>
-      <c r="Q86" s="222"/>
-      <c r="R86" s="222"/>
-      <c r="S86" s="222"/>
-      <c r="T86" s="222"/>
-      <c r="U86" s="222"/>
-      <c r="V86" s="222"/>
-      <c r="W86" s="222"/>
-      <c r="X86" s="222"/>
-      <c r="Y86" s="222"/>
+      <c r="B86" s="219"/>
+      <c r="C86" s="219"/>
+      <c r="D86" s="219"/>
+      <c r="E86" s="219"/>
+      <c r="F86" s="219"/>
+      <c r="G86" s="219"/>
+      <c r="H86" s="219"/>
+      <c r="I86" s="219"/>
+      <c r="J86" s="219"/>
+      <c r="K86" s="219"/>
+      <c r="L86" s="219"/>
+      <c r="M86" s="219"/>
+      <c r="N86" s="219"/>
+      <c r="O86" s="219"/>
+      <c r="P86" s="219"/>
+      <c r="Q86" s="219"/>
+      <c r="R86" s="219"/>
+      <c r="S86" s="219"/>
+      <c r="T86" s="219"/>
+      <c r="U86" s="219"/>
+      <c r="V86" s="219"/>
+      <c r="W86" s="219"/>
+      <c r="X86" s="219"/>
+      <c r="Y86" s="219"/>
     </row>
     <row r="87" spans="1:43" ht="45" customHeight="1">
-      <c r="B87" s="222"/>
-      <c r="C87" s="222"/>
-      <c r="D87" s="222"/>
-      <c r="E87" s="222"/>
-      <c r="F87" s="222"/>
-      <c r="G87" s="222"/>
-      <c r="H87" s="222"/>
-      <c r="I87" s="222"/>
-      <c r="J87" s="222"/>
-      <c r="K87" s="222"/>
-      <c r="L87" s="222"/>
-      <c r="M87" s="222"/>
-      <c r="N87" s="222"/>
-      <c r="O87" s="222"/>
-      <c r="P87" s="222"/>
-      <c r="Q87" s="222"/>
-      <c r="R87" s="222"/>
-      <c r="S87" s="222"/>
-      <c r="T87" s="222"/>
-      <c r="U87" s="222"/>
-      <c r="V87" s="222"/>
-      <c r="W87" s="222"/>
-      <c r="X87" s="222"/>
-      <c r="Y87" s="222"/>
+      <c r="B87" s="219"/>
+      <c r="C87" s="219"/>
+      <c r="D87" s="219"/>
+      <c r="E87" s="219"/>
+      <c r="F87" s="219"/>
+      <c r="G87" s="219"/>
+      <c r="H87" s="219"/>
+      <c r="I87" s="219"/>
+      <c r="J87" s="219"/>
+      <c r="K87" s="219"/>
+      <c r="L87" s="219"/>
+      <c r="M87" s="219"/>
+      <c r="N87" s="219"/>
+      <c r="O87" s="219"/>
+      <c r="P87" s="219"/>
+      <c r="Q87" s="219"/>
+      <c r="R87" s="219"/>
+      <c r="S87" s="219"/>
+      <c r="T87" s="219"/>
+      <c r="U87" s="219"/>
+      <c r="V87" s="219"/>
+      <c r="W87" s="219"/>
+      <c r="X87" s="219"/>
+      <c r="Y87" s="219"/>
     </row>
     <row r="88" spans="1:43" ht="45" customHeight="1">
-      <c r="B88" s="222"/>
-      <c r="C88" s="222"/>
-      <c r="D88" s="222"/>
-      <c r="E88" s="222"/>
-      <c r="F88" s="222"/>
-      <c r="G88" s="222"/>
-      <c r="H88" s="222"/>
-      <c r="I88" s="222"/>
-      <c r="J88" s="222"/>
-      <c r="K88" s="222"/>
-      <c r="L88" s="222"/>
-      <c r="M88" s="222"/>
-      <c r="N88" s="222"/>
-      <c r="O88" s="222"/>
-      <c r="P88" s="222"/>
-      <c r="Q88" s="222"/>
-      <c r="R88" s="222"/>
-      <c r="S88" s="222"/>
-      <c r="T88" s="222"/>
-      <c r="U88" s="222"/>
-      <c r="V88" s="222"/>
-      <c r="W88" s="222"/>
-      <c r="X88" s="222"/>
-      <c r="Y88" s="222"/>
+      <c r="B88" s="219"/>
+      <c r="C88" s="219"/>
+      <c r="D88" s="219"/>
+      <c r="E88" s="219"/>
+      <c r="F88" s="219"/>
+      <c r="G88" s="219"/>
+      <c r="H88" s="219"/>
+      <c r="I88" s="219"/>
+      <c r="J88" s="219"/>
+      <c r="K88" s="219"/>
+      <c r="L88" s="219"/>
+      <c r="M88" s="219"/>
+      <c r="N88" s="219"/>
+      <c r="O88" s="219"/>
+      <c r="P88" s="219"/>
+      <c r="Q88" s="219"/>
+      <c r="R88" s="219"/>
+      <c r="S88" s="219"/>
+      <c r="T88" s="219"/>
+      <c r="U88" s="219"/>
+      <c r="V88" s="219"/>
+      <c r="W88" s="219"/>
+      <c r="X88" s="219"/>
+      <c r="Y88" s="219"/>
     </row>
     <row r="89" spans="1:43" ht="45" customHeight="1">
-      <c r="B89" s="222"/>
-      <c r="C89" s="222"/>
-      <c r="D89" s="222"/>
-      <c r="E89" s="222"/>
-      <c r="F89" s="222"/>
-      <c r="G89" s="222"/>
-      <c r="H89" s="222"/>
-      <c r="I89" s="222"/>
-      <c r="J89" s="222"/>
-      <c r="K89" s="222"/>
-      <c r="L89" s="222"/>
-      <c r="M89" s="222"/>
-      <c r="N89" s="222"/>
-      <c r="O89" s="222"/>
-      <c r="P89" s="222"/>
-      <c r="Q89" s="222"/>
-      <c r="R89" s="222"/>
-      <c r="S89" s="222"/>
-      <c r="T89" s="222"/>
-      <c r="U89" s="222"/>
-      <c r="V89" s="222"/>
-      <c r="W89" s="222"/>
-      <c r="X89" s="222"/>
-      <c r="Y89" s="222"/>
+      <c r="B89" s="219"/>
+      <c r="C89" s="219"/>
+      <c r="D89" s="219"/>
+      <c r="E89" s="219"/>
+      <c r="F89" s="219"/>
+      <c r="G89" s="219"/>
+      <c r="H89" s="219"/>
+      <c r="I89" s="219"/>
+      <c r="J89" s="219"/>
+      <c r="K89" s="219"/>
+      <c r="L89" s="219"/>
+      <c r="M89" s="219"/>
+      <c r="N89" s="219"/>
+      <c r="O89" s="219"/>
+      <c r="P89" s="219"/>
+      <c r="Q89" s="219"/>
+      <c r="R89" s="219"/>
+      <c r="S89" s="219"/>
+      <c r="T89" s="219"/>
+      <c r="U89" s="219"/>
+      <c r="V89" s="219"/>
+      <c r="W89" s="219"/>
+      <c r="X89" s="219"/>
+      <c r="Y89" s="219"/>
     </row>
     <row r="90" spans="1:43" ht="45" customHeight="1">
-      <c r="B90" s="222"/>
-      <c r="C90" s="222"/>
-      <c r="D90" s="222"/>
-      <c r="E90" s="222"/>
-      <c r="F90" s="222"/>
-      <c r="G90" s="222"/>
-      <c r="H90" s="222"/>
-      <c r="I90" s="222"/>
-      <c r="J90" s="222"/>
-      <c r="K90" s="222"/>
-      <c r="L90" s="222"/>
-      <c r="M90" s="222"/>
-      <c r="N90" s="222"/>
-      <c r="O90" s="222"/>
-      <c r="P90" s="222"/>
-      <c r="Q90" s="222"/>
-      <c r="R90" s="222"/>
-      <c r="S90" s="222"/>
-      <c r="T90" s="222"/>
-      <c r="U90" s="222"/>
-      <c r="V90" s="222"/>
-      <c r="W90" s="222"/>
-      <c r="X90" s="222"/>
-      <c r="Y90" s="222"/>
+      <c r="B90" s="219"/>
+      <c r="C90" s="219"/>
+      <c r="D90" s="219"/>
+      <c r="E90" s="219"/>
+      <c r="F90" s="219"/>
+      <c r="G90" s="219"/>
+      <c r="H90" s="219"/>
+      <c r="I90" s="219"/>
+      <c r="J90" s="219"/>
+      <c r="K90" s="219"/>
+      <c r="L90" s="219"/>
+      <c r="M90" s="219"/>
+      <c r="N90" s="219"/>
+      <c r="O90" s="219"/>
+      <c r="P90" s="219"/>
+      <c r="Q90" s="219"/>
+      <c r="R90" s="219"/>
+      <c r="S90" s="219"/>
+      <c r="T90" s="219"/>
+      <c r="U90" s="219"/>
+      <c r="V90" s="219"/>
+      <c r="W90" s="219"/>
+      <c r="X90" s="219"/>
+      <c r="Y90" s="219"/>
     </row>
     <row r="91" spans="1:43" ht="45" customHeight="1">
-      <c r="B91" s="222"/>
-      <c r="C91" s="222"/>
-      <c r="D91" s="222"/>
-      <c r="E91" s="222"/>
-      <c r="F91" s="222"/>
-      <c r="G91" s="222"/>
-      <c r="H91" s="222"/>
-      <c r="I91" s="222"/>
-      <c r="J91" s="222"/>
-      <c r="K91" s="222"/>
-      <c r="L91" s="222"/>
-      <c r="M91" s="222"/>
-      <c r="N91" s="222"/>
-      <c r="O91" s="222"/>
-      <c r="P91" s="222"/>
-      <c r="Q91" s="222"/>
-      <c r="R91" s="222"/>
-      <c r="S91" s="222"/>
-      <c r="T91" s="222"/>
-      <c r="U91" s="222"/>
-      <c r="V91" s="222"/>
-      <c r="W91" s="222"/>
-      <c r="X91" s="222"/>
-      <c r="Y91" s="222"/>
+      <c r="B91" s="219"/>
+      <c r="C91" s="219"/>
+      <c r="D91" s="219"/>
+      <c r="E91" s="219"/>
+      <c r="F91" s="219"/>
+      <c r="G91" s="219"/>
+      <c r="H91" s="219"/>
+      <c r="I91" s="219"/>
+      <c r="J91" s="219"/>
+      <c r="K91" s="219"/>
+      <c r="L91" s="219"/>
+      <c r="M91" s="219"/>
+      <c r="N91" s="219"/>
+      <c r="O91" s="219"/>
+      <c r="P91" s="219"/>
+      <c r="Q91" s="219"/>
+      <c r="R91" s="219"/>
+      <c r="S91" s="219"/>
+      <c r="T91" s="219"/>
+      <c r="U91" s="219"/>
+      <c r="V91" s="219"/>
+      <c r="W91" s="219"/>
+      <c r="X91" s="219"/>
+      <c r="Y91" s="219"/>
     </row>
     <row r="92" spans="1:43" ht="45" customHeight="1">
-      <c r="B92" s="222"/>
-      <c r="C92" s="222"/>
-      <c r="D92" s="222"/>
-      <c r="E92" s="222"/>
-      <c r="F92" s="222"/>
-      <c r="G92" s="222"/>
-      <c r="H92" s="222"/>
-      <c r="I92" s="222"/>
-      <c r="J92" s="222"/>
-      <c r="K92" s="222"/>
-      <c r="L92" s="222"/>
-      <c r="M92" s="222"/>
-      <c r="N92" s="222"/>
-      <c r="O92" s="222"/>
-      <c r="P92" s="222"/>
-      <c r="Q92" s="222"/>
-      <c r="R92" s="222"/>
-      <c r="S92" s="222"/>
-      <c r="T92" s="222"/>
-      <c r="U92" s="222"/>
-      <c r="V92" s="222"/>
-      <c r="W92" s="222"/>
-      <c r="X92" s="222"/>
-      <c r="Y92" s="222"/>
+      <c r="B92" s="219"/>
+      <c r="C92" s="219"/>
+      <c r="D92" s="219"/>
+      <c r="E92" s="219"/>
+      <c r="F92" s="219"/>
+      <c r="G92" s="219"/>
+      <c r="H92" s="219"/>
+      <c r="I92" s="219"/>
+      <c r="J92" s="219"/>
+      <c r="K92" s="219"/>
+      <c r="L92" s="219"/>
+      <c r="M92" s="219"/>
+      <c r="N92" s="219"/>
+      <c r="O92" s="219"/>
+      <c r="P92" s="219"/>
+      <c r="Q92" s="219"/>
+      <c r="R92" s="219"/>
+      <c r="S92" s="219"/>
+      <c r="T92" s="219"/>
+      <c r="U92" s="219"/>
+      <c r="V92" s="219"/>
+      <c r="W92" s="219"/>
+      <c r="X92" s="219"/>
+      <c r="Y92" s="219"/>
     </row>
     <row r="93" spans="1:43" ht="45" customHeight="1">
-      <c r="B93" s="222"/>
-      <c r="C93" s="222"/>
-      <c r="D93" s="222"/>
-      <c r="E93" s="222"/>
-      <c r="F93" s="222"/>
-      <c r="G93" s="222"/>
-      <c r="H93" s="222"/>
-      <c r="I93" s="222"/>
-      <c r="J93" s="222"/>
-      <c r="K93" s="222"/>
-      <c r="L93" s="222"/>
-      <c r="M93" s="222"/>
-      <c r="N93" s="222"/>
-      <c r="O93" s="222"/>
-      <c r="P93" s="222"/>
-      <c r="Q93" s="222"/>
-      <c r="R93" s="222"/>
-      <c r="S93" s="222"/>
-      <c r="T93" s="222"/>
-      <c r="U93" s="222"/>
-      <c r="V93" s="222"/>
-      <c r="W93" s="222"/>
-      <c r="X93" s="222"/>
-      <c r="Y93" s="222"/>
+      <c r="B93" s="219"/>
+      <c r="C93" s="219"/>
+      <c r="D93" s="219"/>
+      <c r="E93" s="219"/>
+      <c r="F93" s="219"/>
+      <c r="G93" s="219"/>
+      <c r="H93" s="219"/>
+      <c r="I93" s="219"/>
+      <c r="J93" s="219"/>
+      <c r="K93" s="219"/>
+      <c r="L93" s="219"/>
+      <c r="M93" s="219"/>
+      <c r="N93" s="219"/>
+      <c r="O93" s="219"/>
+      <c r="P93" s="219"/>
+      <c r="Q93" s="219"/>
+      <c r="R93" s="219"/>
+      <c r="S93" s="219"/>
+      <c r="T93" s="219"/>
+      <c r="U93" s="219"/>
+      <c r="V93" s="219"/>
+      <c r="W93" s="219"/>
+      <c r="X93" s="219"/>
+      <c r="Y93" s="219"/>
     </row>
     <row r="94" spans="1:43" ht="45" customHeight="1">
-      <c r="B94" s="222"/>
-      <c r="C94" s="222"/>
-      <c r="D94" s="222"/>
-      <c r="E94" s="222"/>
-      <c r="F94" s="222"/>
-      <c r="G94" s="222"/>
-      <c r="H94" s="222"/>
-      <c r="I94" s="222"/>
-      <c r="J94" s="222"/>
-      <c r="K94" s="222"/>
-      <c r="L94" s="222"/>
-      <c r="M94" s="222"/>
-      <c r="N94" s="222"/>
-      <c r="O94" s="222"/>
-      <c r="P94" s="222"/>
-      <c r="Q94" s="222"/>
-      <c r="R94" s="222"/>
-      <c r="S94" s="222"/>
-      <c r="T94" s="222"/>
-      <c r="U94" s="222"/>
-      <c r="V94" s="222"/>
-      <c r="W94" s="222"/>
-      <c r="X94" s="222"/>
-      <c r="Y94" s="222"/>
+      <c r="B94" s="219"/>
+      <c r="C94" s="219"/>
+      <c r="D94" s="219"/>
+      <c r="E94" s="219"/>
+      <c r="F94" s="219"/>
+      <c r="G94" s="219"/>
+      <c r="H94" s="219"/>
+      <c r="I94" s="219"/>
+      <c r="J94" s="219"/>
+      <c r="K94" s="219"/>
+      <c r="L94" s="219"/>
+      <c r="M94" s="219"/>
+      <c r="N94" s="219"/>
+      <c r="O94" s="219"/>
+      <c r="P94" s="219"/>
+      <c r="Q94" s="219"/>
+      <c r="R94" s="219"/>
+      <c r="S94" s="219"/>
+      <c r="T94" s="219"/>
+      <c r="U94" s="219"/>
+      <c r="V94" s="219"/>
+      <c r="W94" s="219"/>
+      <c r="X94" s="219"/>
+      <c r="Y94" s="219"/>
     </row>
     <row r="95" spans="1:43" ht="45" customHeight="1">
-      <c r="B95" s="222"/>
-      <c r="C95" s="222"/>
-      <c r="D95" s="222"/>
-      <c r="E95" s="222"/>
-      <c r="F95" s="222"/>
-      <c r="G95" s="222"/>
-      <c r="H95" s="222"/>
-      <c r="I95" s="222"/>
-      <c r="J95" s="222"/>
-      <c r="K95" s="222"/>
-      <c r="L95" s="222"/>
-      <c r="M95" s="222"/>
-      <c r="N95" s="222"/>
-      <c r="O95" s="222"/>
-      <c r="P95" s="222"/>
-      <c r="Q95" s="222"/>
-      <c r="R95" s="222"/>
-      <c r="S95" s="222"/>
-      <c r="T95" s="222"/>
-      <c r="U95" s="222"/>
-      <c r="V95" s="222"/>
-      <c r="W95" s="222"/>
-      <c r="X95" s="222"/>
-      <c r="Y95" s="222"/>
+      <c r="B95" s="219"/>
+      <c r="C95" s="219"/>
+      <c r="D95" s="219"/>
+      <c r="E95" s="219"/>
+      <c r="F95" s="219"/>
+      <c r="G95" s="219"/>
+      <c r="H95" s="219"/>
+      <c r="I95" s="219"/>
+      <c r="J95" s="219"/>
+      <c r="K95" s="219"/>
+      <c r="L95" s="219"/>
+      <c r="M95" s="219"/>
+      <c r="N95" s="219"/>
+      <c r="O95" s="219"/>
+      <c r="P95" s="219"/>
+      <c r="Q95" s="219"/>
+      <c r="R95" s="219"/>
+      <c r="S95" s="219"/>
+      <c r="T95" s="219"/>
+      <c r="U95" s="219"/>
+      <c r="V95" s="219"/>
+      <c r="W95" s="219"/>
+      <c r="X95" s="219"/>
+      <c r="Y95" s="219"/>
     </row>
     <row r="96" spans="1:43" ht="45" customHeight="1">
-      <c r="B96" s="222"/>
-      <c r="C96" s="222"/>
-      <c r="D96" s="222"/>
-      <c r="E96" s="222"/>
-      <c r="F96" s="222"/>
-      <c r="G96" s="222"/>
-      <c r="H96" s="222"/>
-      <c r="I96" s="222"/>
-      <c r="J96" s="222"/>
-      <c r="K96" s="222"/>
-      <c r="L96" s="222"/>
-      <c r="M96" s="222"/>
-      <c r="N96" s="222"/>
-      <c r="O96" s="222"/>
-      <c r="P96" s="222"/>
-      <c r="Q96" s="222"/>
-      <c r="R96" s="222"/>
-      <c r="S96" s="222"/>
-      <c r="T96" s="222"/>
-      <c r="U96" s="222"/>
-      <c r="V96" s="222"/>
-      <c r="W96" s="222"/>
-      <c r="X96" s="222"/>
-      <c r="Y96" s="222"/>
+      <c r="B96" s="219"/>
+      <c r="C96" s="219"/>
+      <c r="D96" s="219"/>
+      <c r="E96" s="219"/>
+      <c r="F96" s="219"/>
+      <c r="G96" s="219"/>
+      <c r="H96" s="219"/>
+      <c r="I96" s="219"/>
+      <c r="J96" s="219"/>
+      <c r="K96" s="219"/>
+      <c r="L96" s="219"/>
+      <c r="M96" s="219"/>
+      <c r="N96" s="219"/>
+      <c r="O96" s="219"/>
+      <c r="P96" s="219"/>
+      <c r="Q96" s="219"/>
+      <c r="R96" s="219"/>
+      <c r="S96" s="219"/>
+      <c r="T96" s="219"/>
+      <c r="U96" s="219"/>
+      <c r="V96" s="219"/>
+      <c r="W96" s="219"/>
+      <c r="X96" s="219"/>
+      <c r="Y96" s="219"/>
     </row>
     <row r="97" spans="2:25" ht="45" customHeight="1">
-      <c r="B97" s="222"/>
-      <c r="C97" s="222"/>
-      <c r="D97" s="222"/>
-      <c r="E97" s="222"/>
-      <c r="F97" s="222"/>
-      <c r="G97" s="222"/>
-      <c r="H97" s="222"/>
-      <c r="I97" s="222"/>
-      <c r="J97" s="222"/>
-      <c r="K97" s="222"/>
-      <c r="L97" s="222"/>
-      <c r="M97" s="222"/>
-      <c r="N97" s="222"/>
-      <c r="O97" s="222"/>
-      <c r="P97" s="222"/>
-      <c r="Q97" s="222"/>
-      <c r="R97" s="222"/>
-      <c r="S97" s="222"/>
-      <c r="T97" s="222"/>
-      <c r="U97" s="222"/>
-      <c r="V97" s="222"/>
-      <c r="W97" s="222"/>
-      <c r="X97" s="222"/>
-      <c r="Y97" s="222"/>
+      <c r="B97" s="219"/>
+      <c r="C97" s="219"/>
+      <c r="D97" s="219"/>
+      <c r="E97" s="219"/>
+      <c r="F97" s="219"/>
+      <c r="G97" s="219"/>
+      <c r="H97" s="219"/>
+      <c r="I97" s="219"/>
+      <c r="J97" s="219"/>
+      <c r="K97" s="219"/>
+      <c r="L97" s="219"/>
+      <c r="M97" s="219"/>
+      <c r="N97" s="219"/>
+      <c r="O97" s="219"/>
+      <c r="P97" s="219"/>
+      <c r="Q97" s="219"/>
+      <c r="R97" s="219"/>
+      <c r="S97" s="219"/>
+      <c r="T97" s="219"/>
+      <c r="U97" s="219"/>
+      <c r="V97" s="219"/>
+      <c r="W97" s="219"/>
+      <c r="X97" s="219"/>
+      <c r="Y97" s="219"/>
     </row>
     <row r="98" spans="2:25" ht="45" customHeight="1">
-      <c r="B98" s="222"/>
-      <c r="C98" s="222"/>
-      <c r="D98" s="222"/>
-      <c r="E98" s="222"/>
-      <c r="F98" s="222"/>
-      <c r="G98" s="222"/>
-      <c r="H98" s="222"/>
-      <c r="I98" s="222"/>
-      <c r="J98" s="222"/>
-      <c r="K98" s="222"/>
-      <c r="L98" s="222"/>
-      <c r="M98" s="222"/>
-      <c r="N98" s="222"/>
-      <c r="O98" s="222"/>
-      <c r="P98" s="222"/>
-      <c r="Q98" s="222"/>
-      <c r="R98" s="222"/>
-      <c r="S98" s="222"/>
-      <c r="T98" s="222"/>
-      <c r="U98" s="222"/>
-      <c r="V98" s="222"/>
-      <c r="W98" s="222"/>
-      <c r="X98" s="222"/>
-      <c r="Y98" s="222"/>
+      <c r="B98" s="219"/>
+      <c r="C98" s="219"/>
+      <c r="D98" s="219"/>
+      <c r="E98" s="219"/>
+      <c r="F98" s="219"/>
+      <c r="G98" s="219"/>
+      <c r="H98" s="219"/>
+      <c r="I98" s="219"/>
+      <c r="J98" s="219"/>
+      <c r="K98" s="219"/>
+      <c r="L98" s="219"/>
+      <c r="M98" s="219"/>
+      <c r="N98" s="219"/>
+      <c r="O98" s="219"/>
+      <c r="P98" s="219"/>
+      <c r="Q98" s="219"/>
+      <c r="R98" s="219"/>
+      <c r="S98" s="219"/>
+      <c r="T98" s="219"/>
+      <c r="U98" s="219"/>
+      <c r="V98" s="219"/>
+      <c r="W98" s="219"/>
+      <c r="X98" s="219"/>
+      <c r="Y98" s="219"/>
     </row>
     <row r="99" spans="2:25" ht="45" customHeight="1">
-      <c r="B99" s="222"/>
-      <c r="C99" s="222"/>
-      <c r="D99" s="222"/>
-      <c r="E99" s="222"/>
-      <c r="F99" s="222"/>
-      <c r="G99" s="222"/>
-      <c r="H99" s="222"/>
-      <c r="I99" s="222"/>
-      <c r="J99" s="222"/>
-      <c r="K99" s="222"/>
-      <c r="L99" s="222"/>
-      <c r="M99" s="222"/>
-      <c r="N99" s="222"/>
-      <c r="O99" s="222"/>
-      <c r="P99" s="222"/>
-      <c r="Q99" s="222"/>
-      <c r="R99" s="222"/>
-      <c r="S99" s="222"/>
-      <c r="T99" s="222"/>
-      <c r="U99" s="222"/>
-      <c r="V99" s="222"/>
-      <c r="W99" s="222"/>
-      <c r="X99" s="222"/>
-      <c r="Y99" s="222"/>
+      <c r="B99" s="219"/>
+      <c r="C99" s="219"/>
+      <c r="D99" s="219"/>
+      <c r="E99" s="219"/>
+      <c r="F99" s="219"/>
+      <c r="G99" s="219"/>
+      <c r="H99" s="219"/>
+      <c r="I99" s="219"/>
+      <c r="J99" s="219"/>
+      <c r="K99" s="219"/>
+      <c r="L99" s="219"/>
+      <c r="M99" s="219"/>
+      <c r="N99" s="219"/>
+      <c r="O99" s="219"/>
+      <c r="P99" s="219"/>
+      <c r="Q99" s="219"/>
+      <c r="R99" s="219"/>
+      <c r="S99" s="219"/>
+      <c r="T99" s="219"/>
+      <c r="U99" s="219"/>
+      <c r="V99" s="219"/>
+      <c r="W99" s="219"/>
+      <c r="X99" s="219"/>
+      <c r="Y99" s="219"/>
     </row>
     <row r="100" spans="2:25" ht="45" customHeight="1">
-      <c r="B100" s="222"/>
-      <c r="C100" s="222"/>
-      <c r="D100" s="222"/>
-      <c r="E100" s="222"/>
-      <c r="F100" s="222"/>
-      <c r="G100" s="222"/>
-      <c r="H100" s="222"/>
-      <c r="I100" s="222"/>
-      <c r="J100" s="222"/>
-      <c r="K100" s="222"/>
-      <c r="L100" s="222"/>
-      <c r="M100" s="222"/>
-      <c r="N100" s="222"/>
-      <c r="O100" s="222"/>
-      <c r="P100" s="222"/>
-      <c r="Q100" s="222"/>
-      <c r="R100" s="222"/>
-      <c r="S100" s="222"/>
-      <c r="T100" s="222"/>
-      <c r="U100" s="222"/>
-      <c r="V100" s="222"/>
-      <c r="W100" s="222"/>
-      <c r="X100" s="222"/>
-      <c r="Y100" s="222"/>
+      <c r="B100" s="219"/>
+      <c r="C100" s="219"/>
+      <c r="D100" s="219"/>
+      <c r="E100" s="219"/>
+      <c r="F100" s="219"/>
+      <c r="G100" s="219"/>
+      <c r="H100" s="219"/>
+      <c r="I100" s="219"/>
+      <c r="J100" s="219"/>
+      <c r="K100" s="219"/>
+      <c r="L100" s="219"/>
+      <c r="M100" s="219"/>
+      <c r="N100" s="219"/>
+      <c r="O100" s="219"/>
+      <c r="P100" s="219"/>
+      <c r="Q100" s="219"/>
+      <c r="R100" s="219"/>
+      <c r="S100" s="219"/>
+      <c r="T100" s="219"/>
+      <c r="U100" s="219"/>
+      <c r="V100" s="219"/>
+      <c r="W100" s="219"/>
+      <c r="X100" s="219"/>
+      <c r="Y100" s="219"/>
     </row>
     <row r="101" spans="2:25" ht="45" customHeight="1">
-      <c r="B101" s="222"/>
-      <c r="C101" s="222"/>
-      <c r="D101" s="222"/>
-      <c r="E101" s="222"/>
-      <c r="F101" s="222"/>
-      <c r="G101" s="222"/>
-      <c r="H101" s="222"/>
-      <c r="I101" s="222"/>
-      <c r="J101" s="222"/>
-      <c r="K101" s="222"/>
-      <c r="L101" s="222"/>
-      <c r="M101" s="222"/>
-      <c r="N101" s="222"/>
-      <c r="O101" s="222"/>
-      <c r="P101" s="222"/>
-      <c r="Q101" s="222"/>
-      <c r="R101" s="222"/>
-      <c r="S101" s="222"/>
-      <c r="T101" s="222"/>
-      <c r="U101" s="222"/>
-      <c r="V101" s="222"/>
-      <c r="W101" s="222"/>
-      <c r="X101" s="222"/>
-      <c r="Y101" s="222"/>
+      <c r="B101" s="219"/>
+      <c r="C101" s="219"/>
+      <c r="D101" s="219"/>
+      <c r="E101" s="219"/>
+      <c r="F101" s="219"/>
+      <c r="G101" s="219"/>
+      <c r="H101" s="219"/>
+      <c r="I101" s="219"/>
+      <c r="J101" s="219"/>
+      <c r="K101" s="219"/>
+      <c r="L101" s="219"/>
+      <c r="M101" s="219"/>
+      <c r="N101" s="219"/>
+      <c r="O101" s="219"/>
+      <c r="P101" s="219"/>
+      <c r="Q101" s="219"/>
+      <c r="R101" s="219"/>
+      <c r="S101" s="219"/>
+      <c r="T101" s="219"/>
+      <c r="U101" s="219"/>
+      <c r="V101" s="219"/>
+      <c r="W101" s="219"/>
+      <c r="X101" s="219"/>
+      <c r="Y101" s="219"/>
     </row>
     <row r="102" spans="2:25" ht="45" customHeight="1">
-      <c r="B102" s="222"/>
-      <c r="C102" s="222"/>
-      <c r="D102" s="222"/>
-      <c r="E102" s="222"/>
-      <c r="F102" s="222"/>
-      <c r="G102" s="222"/>
-      <c r="H102" s="222"/>
-      <c r="I102" s="222"/>
-      <c r="J102" s="222"/>
-      <c r="K102" s="222"/>
-      <c r="L102" s="222"/>
-      <c r="M102" s="222"/>
-      <c r="N102" s="222"/>
-      <c r="O102" s="222"/>
-      <c r="P102" s="222"/>
-      <c r="Q102" s="222"/>
-      <c r="R102" s="222"/>
-      <c r="S102" s="222"/>
-      <c r="T102" s="222"/>
-      <c r="U102" s="222"/>
-      <c r="V102" s="222"/>
-      <c r="W102" s="222"/>
-      <c r="X102" s="222"/>
-      <c r="Y102" s="222"/>
+      <c r="B102" s="219"/>
+      <c r="C102" s="219"/>
+      <c r="D102" s="219"/>
+      <c r="E102" s="219"/>
+      <c r="F102" s="219"/>
+      <c r="G102" s="219"/>
+      <c r="H102" s="219"/>
+      <c r="I102" s="219"/>
+      <c r="J102" s="219"/>
+      <c r="K102" s="219"/>
+      <c r="L102" s="219"/>
+      <c r="M102" s="219"/>
+      <c r="N102" s="219"/>
+      <c r="O102" s="219"/>
+      <c r="P102" s="219"/>
+      <c r="Q102" s="219"/>
+      <c r="R102" s="219"/>
+      <c r="S102" s="219"/>
+      <c r="T102" s="219"/>
+      <c r="U102" s="219"/>
+      <c r="V102" s="219"/>
+      <c r="W102" s="219"/>
+      <c r="X102" s="219"/>
+      <c r="Y102" s="219"/>
     </row>
     <row r="103" spans="2:25" ht="45" customHeight="1">
-      <c r="B103" s="222"/>
-      <c r="C103" s="222"/>
-      <c r="D103" s="222"/>
-      <c r="E103" s="222"/>
-      <c r="F103" s="222"/>
-      <c r="G103" s="222"/>
-      <c r="H103" s="222"/>
-      <c r="I103" s="222"/>
-      <c r="J103" s="222"/>
-      <c r="K103" s="222"/>
-      <c r="L103" s="222"/>
-      <c r="M103" s="222"/>
-      <c r="N103" s="222"/>
-      <c r="O103" s="222"/>
-      <c r="P103" s="222"/>
-      <c r="Q103" s="222"/>
-      <c r="R103" s="222"/>
-      <c r="S103" s="222"/>
-      <c r="T103" s="222"/>
-      <c r="U103" s="222"/>
-      <c r="V103" s="222"/>
-      <c r="W103" s="222"/>
-      <c r="X103" s="222"/>
-      <c r="Y103" s="222"/>
+      <c r="B103" s="219"/>
+      <c r="C103" s="219"/>
+      <c r="D103" s="219"/>
+      <c r="E103" s="219"/>
+      <c r="F103" s="219"/>
+      <c r="G103" s="219"/>
+      <c r="H103" s="219"/>
+      <c r="I103" s="219"/>
+      <c r="J103" s="219"/>
+      <c r="K103" s="219"/>
+      <c r="L103" s="219"/>
+      <c r="M103" s="219"/>
+      <c r="N103" s="219"/>
+      <c r="O103" s="219"/>
+      <c r="P103" s="219"/>
+      <c r="Q103" s="219"/>
+      <c r="R103" s="219"/>
+      <c r="S103" s="219"/>
+      <c r="T103" s="219"/>
+      <c r="U103" s="219"/>
+      <c r="V103" s="219"/>
+      <c r="W103" s="219"/>
+      <c r="X103" s="219"/>
+      <c r="Y103" s="219"/>
     </row>
     <row r="104" spans="2:25" ht="45" customHeight="1">
-      <c r="B104" s="222"/>
-      <c r="C104" s="222"/>
-      <c r="D104" s="222"/>
-      <c r="E104" s="222"/>
-      <c r="F104" s="222"/>
-      <c r="G104" s="222"/>
-      <c r="H104" s="222"/>
-      <c r="I104" s="222"/>
-      <c r="J104" s="222"/>
-      <c r="K104" s="222"/>
-      <c r="L104" s="222"/>
-      <c r="M104" s="222"/>
-      <c r="N104" s="222"/>
-      <c r="O104" s="222"/>
-      <c r="P104" s="222"/>
-      <c r="Q104" s="222"/>
-      <c r="R104" s="222"/>
-      <c r="S104" s="222"/>
-      <c r="T104" s="222"/>
-      <c r="U104" s="222"/>
-      <c r="V104" s="222"/>
-      <c r="W104" s="222"/>
-      <c r="X104" s="222"/>
-      <c r="Y104" s="222"/>
+      <c r="B104" s="219"/>
+      <c r="C104" s="219"/>
+      <c r="D104" s="219"/>
+      <c r="E104" s="219"/>
+      <c r="F104" s="219"/>
+      <c r="G104" s="219"/>
+      <c r="H104" s="219"/>
+      <c r="I104" s="219"/>
+      <c r="J104" s="219"/>
+      <c r="K104" s="219"/>
+      <c r="L104" s="219"/>
+      <c r="M104" s="219"/>
+      <c r="N104" s="219"/>
+      <c r="O104" s="219"/>
+      <c r="P104" s="219"/>
+      <c r="Q104" s="219"/>
+      <c r="R104" s="219"/>
+      <c r="S104" s="219"/>
+      <c r="T104" s="219"/>
+      <c r="U104" s="219"/>
+      <c r="V104" s="219"/>
+      <c r="W104" s="219"/>
+      <c r="X104" s="219"/>
+      <c r="Y104" s="219"/>
     </row>
     <row r="105" spans="2:25" ht="45" customHeight="1">
       <c r="B105" s="82"/>
